--- a/database/event/4702/event_4702_evp_summary.xlsx
+++ b/database/event/4702/event_4702_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.1647</v>
+        <v>5.6788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9396</v>
+        <v>1.2811</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2611</v>
+        <v>1.8185</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1647</v>
+        <v>5.6788</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1804</v>
+        <v>4.6945</v>
       </c>
       <c r="G2" t="n">
         <v>0.9843</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1804</v>
+        <v>5.058</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1952</v>
+        <v>5.1005</v>
       </c>
       <c r="J2" t="n">
         <v>0.9843</v>
@@ -529,7 +529,7 @@
         <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1795</v>
+        <v>6.0848</v>
       </c>
       <c r="N2" t="n">
         <v>177</v>
@@ -538,139 +538,139 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.8721</v>
+        <v>4.1049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6479</v>
+        <v>0.9261</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7389</v>
+        <v>1.1915</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8721</v>
+        <v>4.1049</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8721</v>
+        <v>3.5066</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8721</v>
+        <v>3.5066</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8721</v>
+        <v>3.5361</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8721</v>
+        <v>4.134399999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.8716</v>
+        <v>3.6347</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6478</v>
+        <v>0.82</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7387</v>
+        <v>1.0042</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8716</v>
+        <v>3.6347</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8716</v>
+        <v>3.6347</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8716</v>
+        <v>3.6347</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8716</v>
+        <v>3.6347</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8716</v>
+        <v>3.6347</v>
       </c>
       <c r="N4" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7849</v>
+        <v>3.5868</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6283</v>
+        <v>0.8092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7037</v>
+        <v>0.9851</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7849</v>
+        <v>3.5868</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1866</v>
+        <v>3.5868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5983000000000001</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1866</v>
+        <v>3.5868</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1968</v>
+        <v>3.5868</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5983000000000001</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L5" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7951</v>
+        <v>3.5868</v>
       </c>
       <c r="N5" t="n">
-        <v>177</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5523</v>
+        <v>3.0874</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5758</v>
+        <v>0.6965</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6097</v>
+        <v>0.7861</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5523</v>
+        <v>3.0874</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5038</v>
+        <v>2.0389</v>
       </c>
       <c r="G6" t="n">
         <v>1.0485</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5038</v>
+        <v>2.0389</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5108</v>
+        <v>2.0561</v>
       </c>
       <c r="J6" t="n">
         <v>1.0485</v>
@@ -713,7 +713,7 @@
         <v>64</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5593</v>
+        <v>3.1046</v>
       </c>
       <c r="N6" t="n">
         <v>177</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8137</v>
+        <v>2.7112</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4092</v>
+        <v>0.6116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3113</v>
+        <v>0.6362</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8137</v>
+        <v>2.7112</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8137</v>
+        <v>2.7112</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8137</v>
+        <v>2.7112</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8137</v>
+        <v>2.7112</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8137</v>
+        <v>2.7112</v>
       </c>
       <c r="N7" t="n">
         <v>124</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6916</v>
+        <v>2.5569</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3816</v>
+        <v>0.5768</v>
       </c>
       <c r="D8" t="n">
-        <v>0.262</v>
+        <v>0.5748</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6916</v>
+        <v>2.5569</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6001</v>
+        <v>2.5569</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0915</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6001</v>
+        <v>2.5569</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6075</v>
+        <v>2.5569</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0915</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="L8" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.699</v>
+        <v>2.5569</v>
       </c>
       <c r="N8" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5239</v>
+        <v>2.3306</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3438</v>
+        <v>0.5258</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1943</v>
+        <v>0.4846</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5239</v>
+        <v>2.3306</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5239</v>
+        <v>2.2391</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.0915</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5239</v>
+        <v>2.2391</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5239</v>
+        <v>2.2579</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0915</v>
       </c>
       <c r="K9" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5239</v>
+        <v>2.3494</v>
       </c>
       <c r="N9" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3623</v>
+        <v>2.3292</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3073</v>
+        <v>0.5255</v>
       </c>
       <c r="D10" t="n">
-        <v>0.129</v>
+        <v>0.484</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3623</v>
+        <v>2.3292</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2852</v>
+        <v>2.3292</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0771</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2852</v>
+        <v>2.3292</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2852</v>
+        <v>2.3292</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0771</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3623</v>
+        <v>2.3292</v>
       </c>
       <c r="N10" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3576</v>
+        <v>2.1748</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3063</v>
+        <v>0.4906</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1271</v>
+        <v>0.4225</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3576</v>
+        <v>2.1748</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3576</v>
+        <v>2.1748</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3576</v>
+        <v>2.1748</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3576</v>
+        <v>2.1748</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3576</v>
+        <v>2.1748</v>
       </c>
       <c r="N11" t="n">
         <v>124</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.178</v>
+        <v>2.0248</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2658</v>
+        <v>0.4568</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0545</v>
+        <v>0.3628</v>
       </c>
       <c r="E12" t="n">
-        <v>1.178</v>
+        <v>2.0248</v>
       </c>
       <c r="F12" t="n">
-        <v>1.178</v>
+        <v>3.0248</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.178</v>
+        <v>3.0248</v>
       </c>
       <c r="I12" t="n">
-        <v>1.178</v>
+        <v>3.0248</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>1.178</v>
+        <v>2.0248</v>
       </c>
       <c r="N12" t="n">
-        <v>116</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.98</v>
+        <v>1.6124</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2211</v>
+        <v>0.3638</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0255</v>
+        <v>0.1985</v>
       </c>
       <c r="E13" t="n">
-        <v>0.98</v>
+        <v>1.6124</v>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>1.5353</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>0.0771</v>
       </c>
       <c r="H13" t="n">
-        <v>1.98</v>
+        <v>1.5353</v>
       </c>
       <c r="I13" t="n">
-        <v>1.98</v>
+        <v>1.5353</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>0.0771</v>
       </c>
       <c r="K13" t="n">
         <v>117</v>
@@ -1035,7 +1035,7 @@
         <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>0.98</v>
+        <v>1.6124</v>
       </c>
       <c r="N13" t="n">
         <v>181</v>
@@ -1044,173 +1044,173 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7395</v>
+        <v>1.4416</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1668</v>
+        <v>0.3252</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1226</v>
+        <v>0.1304</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7395</v>
+        <v>1.4416</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6832</v>
+        <v>1.4416</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6832</v>
+        <v>1.4416</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6864</v>
+        <v>1.4416</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7427</v>
+        <v>1.4416</v>
       </c>
       <c r="N14" t="n">
-        <v>177</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7083</v>
+        <v>1.4063</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1598</v>
+        <v>0.3173</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1352</v>
+        <v>0.1164</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7083</v>
+        <v>1.4063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7083</v>
+        <v>1.35</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7083</v>
+        <v>1.35</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7083</v>
+        <v>1.3614</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="K15" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7083</v>
+        <v>1.4177</v>
       </c>
       <c r="N15" t="n">
-        <v>116</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6612</v>
+        <v>0.8921</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1492</v>
+        <v>0.2013</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1543</v>
+        <v>-0.0885</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6612</v>
+        <v>0.8921</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6612</v>
+        <v>0.5442</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.3479</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6612</v>
+        <v>0.5442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6612</v>
+        <v>0.5442</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.3479</v>
       </c>
       <c r="K16" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6612</v>
+        <v>0.8921</v>
       </c>
       <c r="N16" t="n">
-        <v>116</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.328</v>
+        <v>0.8383</v>
       </c>
       <c r="C17" t="n">
-        <v>0.074</v>
+        <v>0.1891</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2889</v>
+        <v>-0.1099</v>
       </c>
       <c r="E17" t="n">
-        <v>0.328</v>
+        <v>0.8383</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6344</v>
+        <v>0.7359</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3064</v>
+        <v>0.1024</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6344</v>
+        <v>0.7359</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6344</v>
+        <v>0.7359</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3064</v>
+        <v>0.1024</v>
       </c>
       <c r="K17" t="n">
         <v>117</v>
@@ -1219,7 +1219,7 @@
         <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>0.328</v>
+        <v>0.8383</v>
       </c>
       <c r="N17" t="n">
         <v>181</v>
@@ -1228,127 +1228,127 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2668</v>
+        <v>0.7484</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0602</v>
+        <v>0.1688</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3136</v>
+        <v>-0.1457</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2668</v>
+        <v>0.7484</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1644</v>
+        <v>0.7484</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1024</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1644</v>
+        <v>0.7484</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1644</v>
+        <v>0.7484</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1024</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2668</v>
+        <v>0.7484</v>
       </c>
       <c r="N18" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2024</v>
+        <v>0.7083</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0457</v>
+        <v>0.1598</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3396</v>
+        <v>-0.1617</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2024</v>
+        <v>0.7083</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2024</v>
+        <v>0.7083</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2024</v>
+        <v>0.7083</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2024</v>
+        <v>0.7083</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2024</v>
+        <v>0.7083</v>
       </c>
       <c r="N19" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1715</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0387</v>
+        <v>0.1129</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3521</v>
+        <v>-0.2445</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1715</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1764</v>
+        <v>0.8069</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3479</v>
+        <v>-0.3064</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1764</v>
+        <v>0.8069</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1764</v>
+        <v>0.8069</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3479</v>
+        <v>-0.3064</v>
       </c>
       <c r="K20" t="n">
         <v>117</v>
@@ -1357,7 +1357,7 @@
         <v>64</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1715</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>181</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0182</v>
+        <v>0.426</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0041</v>
+        <v>0.0961</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.414</v>
+        <v>-0.2742</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0182</v>
+        <v>0.426</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0182</v>
+        <v>0.426</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0182</v>
+        <v>0.426</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0182</v>
+        <v>0.426</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0182</v>
+        <v>0.426</v>
       </c>
       <c r="N21" t="n">
         <v>116</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0525</v>
+        <v>0.006</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0118</v>
+        <v>0.0014</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4426</v>
+        <v>-0.4415</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0525</v>
+        <v>0.006</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0525</v>
+        <v>0.006</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0525</v>
+        <v>0.006</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0525</v>
+        <v>0.006</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0525</v>
+        <v>0.006</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7591</v>
+        <v>-0.5877</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1713</v>
+        <v>-0.1326</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.728</v>
+        <v>-0.6781</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7591</v>
+        <v>-0.5877</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7591</v>
+        <v>-0.5877</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7591</v>
+        <v>-0.5877</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7591</v>
+        <v>-0.5877</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7591</v>
+        <v>-0.5877</v>
       </c>
       <c r="N23" t="n">
         <v>141</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.0949</v>
+        <v>-0.7591</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.247</v>
+        <v>-0.1713</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8637</v>
+        <v>-0.7463</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0949</v>
+        <v>-0.7591</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0949</v>
+        <v>-0.7591</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0949</v>
+        <v>-0.7591</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0949</v>
+        <v>-0.7591</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0949</v>
+        <v>-0.7591</v>
       </c>
       <c r="N24" t="n">
         <v>141</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.1586</v>
+        <v>-0.8017</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2614</v>
+        <v>-0.1809</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8894</v>
+        <v>-0.7633</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1586</v>
+        <v>-0.8017</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1586</v>
+        <v>-0.8017</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1586</v>
+        <v>-0.8017</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1586</v>
+        <v>-0.8017</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1586</v>
+        <v>-0.8017</v>
       </c>
       <c r="N25" t="n">
         <v>116</v>
@@ -1606,7 +1606,7 @@
         <v>-0.2658</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8974</v>
+        <v>-0.9133</v>
       </c>
       <c r="E26" t="n">
         <v>-1.1783</v>
@@ -1652,7 +1652,7 @@
         <v>-0.3339</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0193</v>
+        <v>-1.0336</v>
       </c>
       <c r="E27" t="n">
         <v>-1.4802</v>
@@ -1698,7 +1698,7 @@
         <v>-0.3631</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0716</v>
+        <v>-1.0851</v>
       </c>
       <c r="E28" t="n">
         <v>-1.6095</v>
@@ -1744,7 +1744,7 @@
         <v>-0.445</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2182</v>
+        <v>-1.2298</v>
       </c>
       <c r="E29" t="n">
         <v>-1.9726</v>
@@ -1790,7 +1790,7 @@
         <v>-0.4743</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2707</v>
+        <v>-1.2815</v>
       </c>
       <c r="E30" t="n">
         <v>-2.1025</v>
@@ -1836,7 +1836,7 @@
         <v>-0.5106000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3358</v>
+        <v>-1.3457</v>
       </c>
       <c r="E31" t="n">
         <v>-2.2635</v>

--- a/database/event/4702/event_4702_evp_summary.xlsx
+++ b/database/event/4702/event_4702_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6788</v>
+        <v>4.5395</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2811</v>
+        <v>1.0241</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8185</v>
+        <v>1.4113</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6788</v>
+        <v>4.5395</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6945</v>
+        <v>3.56</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9843</v>
+        <v>0.9795</v>
       </c>
       <c r="H2" t="n">
-        <v>5.058</v>
+        <v>4.4574</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1005</v>
+        <v>4.6407</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9843</v>
+        <v>0.9795</v>
       </c>
       <c r="K2" t="n">
         <v>113</v>
@@ -529,7 +529,7 @@
         <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>6.0848</v>
+        <v>5.6202</v>
       </c>
       <c r="N2" t="n">
         <v>177</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1049</v>
+        <v>3.6624</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9261</v>
+        <v>0.8262</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1915</v>
+        <v>1.0154</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1049</v>
+        <v>3.6624</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5066</v>
+        <v>3.011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.6514</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5066</v>
+        <v>3.252</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5361</v>
+        <v>3.3857</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.6514</v>
       </c>
       <c r="K3" t="n">
         <v>113</v>
@@ -575,7 +575,7 @@
         <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>4.134399999999999</v>
+        <v>4.0371</v>
       </c>
       <c r="N3" t="n">
         <v>177</v>
@@ -584,47 +584,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6347</v>
+        <v>3.4667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.82</v>
+        <v>0.7821</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0042</v>
+        <v>0.927</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6347</v>
+        <v>3.4667</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6347</v>
+        <v>2.4432</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.0235</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6347</v>
+        <v>2.4432</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6347</v>
+        <v>2.5437</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.0235</v>
       </c>
       <c r="K4" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6347</v>
+        <v>3.5672</v>
       </c>
       <c r="N4" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5868</v>
+        <v>3.3191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8092</v>
+        <v>0.7488</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9851</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5868</v>
+        <v>3.3191</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5868</v>
+        <v>3.3191</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5868</v>
+        <v>3.9283</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5868</v>
+        <v>3.9283</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5868</v>
+        <v>3.9283</v>
       </c>
       <c r="N5" t="n">
         <v>124</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0874</v>
+        <v>3.2993</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6965</v>
+        <v>0.7443</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7861</v>
+        <v>0.8515</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0874</v>
+        <v>3.2993</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0389</v>
+        <v>3.2993</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0485</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0389</v>
+        <v>3.885</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0561</v>
+        <v>3.885</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0485</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1046</v>
+        <v>3.885</v>
       </c>
       <c r="N6" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7112</v>
+        <v>2.8928</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6116</v>
+        <v>0.6526</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6362</v>
+        <v>0.6679</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7112</v>
+        <v>2.8928</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7112</v>
+        <v>2.8928</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7112</v>
+        <v>2.9924</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7112</v>
+        <v>2.9924</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7112</v>
+        <v>2.9924</v>
       </c>
       <c r="N7" t="n">
         <v>124</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5569</v>
+        <v>2.8159</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5768</v>
+        <v>0.6353</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5748</v>
+        <v>0.6332</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5569</v>
+        <v>2.8159</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5569</v>
+        <v>2.8159</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5569</v>
+        <v>2.8236</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5569</v>
+        <v>2.8236</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5569</v>
+        <v>2.8236</v>
       </c>
       <c r="N8" t="n">
         <v>141</v>
@@ -814,219 +814,219 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3306</v>
+        <v>2.5751</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5258</v>
+        <v>0.5809</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4846</v>
+        <v>0.5245</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3306</v>
+        <v>2.5751</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2391</v>
+        <v>2.5751</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0915</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2391</v>
+        <v>2.5751</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2579</v>
+        <v>2.5751</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0915</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3494</v>
+        <v>2.5751</v>
       </c>
       <c r="N9" t="n">
-        <v>177</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3292</v>
+        <v>2.5642</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5255</v>
+        <v>0.5785</v>
       </c>
       <c r="D10" t="n">
-        <v>0.484</v>
+        <v>0.5196</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3292</v>
+        <v>2.5642</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3292</v>
+        <v>2.3562</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3292</v>
+        <v>2.3562</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3292</v>
+        <v>2.4531</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="K10" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3292</v>
+        <v>2.6611</v>
       </c>
       <c r="N10" t="n">
-        <v>116</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1748</v>
+        <v>2.3314</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4906</v>
+        <v>0.526</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4225</v>
+        <v>0.4145</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1748</v>
+        <v>2.3314</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1748</v>
+        <v>1.8694</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1748</v>
+        <v>1.8694</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1748</v>
+        <v>1.8694</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1748</v>
+        <v>2.3314</v>
       </c>
       <c r="N11" t="n">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0248</v>
+        <v>2.2718</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4568</v>
+        <v>0.5125</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3628</v>
+        <v>0.3876</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0248</v>
+        <v>2.2718</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0248</v>
+        <v>2.2718</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0248</v>
+        <v>2.2718</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0248</v>
+        <v>2.2718</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="L12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0248</v>
+        <v>2.2718</v>
       </c>
       <c r="N12" t="n">
-        <v>181</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6124</v>
+        <v>2.2113</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3638</v>
+        <v>0.4989</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1985</v>
+        <v>0.3603</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6124</v>
+        <v>2.2113</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5353</v>
+        <v>2.9507</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0771</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5353</v>
+        <v>3.1194</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5353</v>
+        <v>3.1194</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0771</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>117</v>
@@ -1035,7 +1035,7 @@
         <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6124</v>
+        <v>2.38</v>
       </c>
       <c r="N13" t="n">
         <v>181</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4416</v>
+        <v>1.7911</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3252</v>
+        <v>0.4041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1304</v>
+        <v>0.1706</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4416</v>
+        <v>1.7911</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4416</v>
+        <v>1.7911</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4416</v>
+        <v>1.7911</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4416</v>
+        <v>1.7911</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4416</v>
+        <v>1.7911</v>
       </c>
       <c r="N14" t="n">
         <v>124</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4063</v>
+        <v>1.71</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3173</v>
+        <v>0.3858</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1164</v>
+        <v>0.134</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4063</v>
+        <v>1.71</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35</v>
+        <v>1.6326</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0563</v>
+        <v>0.0774</v>
       </c>
       <c r="H15" t="n">
-        <v>1.35</v>
+        <v>1.6326</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3614</v>
+        <v>1.6997</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0563</v>
+        <v>0.0774</v>
       </c>
       <c r="K15" t="n">
         <v>113</v>
@@ -1127,7 +1127,7 @@
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4177</v>
+        <v>1.7771</v>
       </c>
       <c r="N15" t="n">
         <v>177</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8921</v>
+        <v>1.3763</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2013</v>
+        <v>0.3105</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0885</v>
+        <v>-0.0167</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8921</v>
+        <v>1.3763</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5442</v>
+        <v>0.834</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3479</v>
+        <v>0.5423</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5442</v>
+        <v>0.834</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5442</v>
+        <v>0.834</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3479</v>
+        <v>0.5423</v>
       </c>
       <c r="K16" t="n">
         <v>117</v>
@@ -1173,7 +1173,7 @@
         <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8921</v>
+        <v>1.3763</v>
       </c>
       <c r="N16" t="n">
         <v>181</v>
@@ -1182,216 +1182,216 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8383</v>
+        <v>1.2326</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1891</v>
+        <v>0.2781</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1099</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8383</v>
+        <v>1.2326</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7359</v>
+        <v>1.2326</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1024</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7359</v>
+        <v>1.2326</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7359</v>
+        <v>1.2326</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1024</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8383</v>
+        <v>1.2326</v>
       </c>
       <c r="N17" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7484</v>
+        <v>1.184</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1688</v>
+        <v>0.2671</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1457</v>
+        <v>-0.1035</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7484</v>
+        <v>1.184</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7484</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7484</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7484</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="K18" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7484</v>
+        <v>1.184</v>
       </c>
       <c r="N18" t="n">
-        <v>116</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7083</v>
+        <v>1.1535</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1598</v>
+        <v>0.2602</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1617</v>
+        <v>-0.1173</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7083</v>
+        <v>1.1535</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7083</v>
+        <v>1.3532</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.1997</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7083</v>
+        <v>1.3532</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7083</v>
+        <v>1.3532</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.1997</v>
       </c>
       <c r="K19" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7083</v>
+        <v>1.1535</v>
       </c>
       <c r="N19" t="n">
-        <v>116</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5004999999999999</v>
+        <v>1.0195</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1129</v>
+        <v>0.23</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2445</v>
+        <v>-0.1778</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5004999999999999</v>
+        <v>1.0195</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8069</v>
+        <v>1.0195</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3064</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8069</v>
+        <v>1.0195</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8069</v>
+        <v>1.0195</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3064</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L20" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5004999999999999</v>
+        <v>1.0195</v>
       </c>
       <c r="N20" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.426</v>
+        <v>1.0087</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0961</v>
+        <v>0.2276</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2742</v>
+        <v>-0.1826</v>
       </c>
       <c r="E21" t="n">
-        <v>0.426</v>
+        <v>1.0087</v>
       </c>
       <c r="F21" t="n">
-        <v>0.426</v>
+        <v>1.0087</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.426</v>
+        <v>1.0087</v>
       </c>
       <c r="I21" t="n">
-        <v>0.426</v>
+        <v>1.0087</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.426</v>
+        <v>1.0087</v>
       </c>
       <c r="N21" t="n">
         <v>116</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0014</v>
+        <v>0.157</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4415</v>
+        <v>-0.3238</v>
       </c>
       <c r="E22" t="n">
-        <v>0.006</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.006</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.006</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.006</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.006</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1458,78 +1458,78 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5877</v>
+        <v>-0.179</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1326</v>
+        <v>-0.0404</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6781</v>
+        <v>-0.7188</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5877</v>
+        <v>-0.179</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5877</v>
+        <v>-0.179</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5877</v>
+        <v>-0.179</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5877</v>
+        <v>-0.179</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5877</v>
+        <v>-0.179</v>
       </c>
       <c r="N23" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.7591</v>
+        <v>-0.2381</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1713</v>
+        <v>-0.0537</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7463</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7591</v>
+        <v>-0.2381</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7591</v>
+        <v>-0.2381</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7591</v>
+        <v>-0.2381</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7591</v>
+        <v>-0.2381</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7591</v>
+        <v>-0.2381</v>
       </c>
       <c r="N24" t="n">
         <v>141</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.8017</v>
+        <v>-0.3329</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1809</v>
+        <v>-0.0751</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7633</v>
+        <v>-0.7883</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8017</v>
+        <v>-0.3329</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8017</v>
+        <v>-0.3329</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8017</v>
+        <v>-0.3329</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8017</v>
+        <v>-0.3329</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8017</v>
+        <v>-0.3329</v>
       </c>
       <c r="N25" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.1783</v>
+        <v>-0.6693</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2658</v>
+        <v>-0.151</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9133</v>
+        <v>-0.9402</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1783</v>
+        <v>-0.6693</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1783</v>
+        <v>-0.6693</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1783</v>
+        <v>-0.6693</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.1783</v>
+        <v>-0.6693</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1783</v>
+        <v>-0.6693</v>
       </c>
       <c r="N26" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.4802</v>
+        <v>-0.8171</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3339</v>
+        <v>-0.1843</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0336</v>
+        <v>-1.0069</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.4802</v>
+        <v>-0.8171</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4802</v>
+        <v>-0.8171</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.4802</v>
+        <v>-0.8171</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.4802</v>
+        <v>-0.8171</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.4802</v>
+        <v>-0.8171</v>
       </c>
       <c r="N27" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.6095</v>
+        <v>-1.2101</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3631</v>
+        <v>-0.273</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0851</v>
+        <v>-1.1843</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.6095</v>
+        <v>-1.2101</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.6095</v>
+        <v>-1.2101</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.6095</v>
+        <v>-1.2101</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.6095</v>
+        <v>-1.2101</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.6095</v>
+        <v>-1.2101</v>
       </c>
       <c r="N28" t="n">
         <v>121</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.9726</v>
+        <v>-1.3543</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.445</v>
+        <v>-0.3055</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2298</v>
+        <v>-1.2494</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9726</v>
+        <v>-1.3543</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.9726</v>
+        <v>-1.3543</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.9726</v>
+        <v>-1.3543</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.9726</v>
+        <v>-1.3543</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.9726</v>
+        <v>-1.3543</v>
       </c>
       <c r="N29" t="n">
         <v>121</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.1025</v>
+        <v>-1.4603</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4743</v>
+        <v>-0.3294</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2815</v>
+        <v>-1.2973</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.1025</v>
+        <v>-1.4603</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.1025</v>
+        <v>-1.4603</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.1025</v>
+        <v>-1.4603</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.1025</v>
+        <v>-1.4603</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.1025</v>
+        <v>-1.4603</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.2635</v>
+        <v>-1.6602</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.3745</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3457</v>
+        <v>-1.3875</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.2635</v>
+        <v>-1.6602</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.2635</v>
+        <v>-1.6602</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.2635</v>
+        <v>-1.6602</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.2635</v>
+        <v>-1.6602</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.2635</v>
+        <v>-1.6602</v>
       </c>
       <c r="N31" t="n">
         <v>121</v>
@@ -1969,10 +1969,10 @@
         <v>1.26</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7872</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>28.3392</v>
+        <v>27.126</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1947</v>
+        <v>0.1871</v>
       </c>
       <c r="J3" t="n">
-        <v>7.0092</v>
+        <v>6.7356</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1516</v>
+        <v>-0.1041</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.4576</v>
+        <v>-3.7476</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.97</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1913</v>
+        <v>-0.141</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.8868</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2281</v>
+        <v>-0.1758</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.211600000000001</v>
+        <v>-6.3288</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>0.718</v>
+        <v>0.8885</v>
       </c>
       <c r="J7" t="n">
-        <v>25.848</v>
+        <v>31.986</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.95</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1346</v>
+        <v>-0.0757</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.8456</v>
+        <v>-2.7252</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2099</v>
+        <v>-0.1228</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.5564</v>
+        <v>-4.4208</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2607</v>
+        <v>-0.1559</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.385199999999999</v>
+        <v>-5.6124</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3975</v>
+        <v>-0.2488</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.31</v>
+        <v>-8.956799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.49</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2001</v>
+        <v>1.1276</v>
       </c>
       <c r="J12" t="n">
-        <v>33.6028</v>
+        <v>31.5728</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7896</v>
+        <v>0.7924</v>
       </c>
       <c r="J13" t="n">
-        <v>22.1088</v>
+        <v>22.1872</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7896</v>
+        <v>0.7924</v>
       </c>
       <c r="J14" t="n">
-        <v>22.1088</v>
+        <v>22.1872</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3196</v>
+        <v>0.3838</v>
       </c>
       <c r="J15" t="n">
-        <v>8.9488</v>
+        <v>10.7464</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7309</v>
+        <v>-0.6761</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.4652</v>
+        <v>-18.9308</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5578</v>
+        <v>0.6651</v>
       </c>
       <c r="J17" t="n">
-        <v>15.6184</v>
+        <v>18.6228</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3631</v>
+        <v>0.4019</v>
       </c>
       <c r="J18" t="n">
-        <v>10.1668</v>
+        <v>11.2532</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1718</v>
+        <v>-0.124</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.8104</v>
+        <v>-3.472</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6409</v>
+        <v>-0.4265</v>
       </c>
       <c r="J20" t="n">
-        <v>-17.9452</v>
+        <v>-11.942</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7264</v>
+        <v>-0.4906</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.3392</v>
+        <v>-13.7368</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.68</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5129</v>
+        <v>1.3367</v>
       </c>
       <c r="J22" t="n">
-        <v>39.3354</v>
+        <v>34.7542</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.59</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3435</v>
+        <v>1.2278</v>
       </c>
       <c r="J23" t="n">
-        <v>34.931</v>
+        <v>31.9228</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8998</v>
       </c>
       <c r="J24" t="n">
-        <v>22.4224</v>
+        <v>23.3948</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3736</v>
+        <v>0.463</v>
       </c>
       <c r="J25" t="n">
-        <v>9.7136</v>
+        <v>12.038</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.801</v>
+        <v>-0.7516</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.826</v>
+        <v>-19.5416</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4429</v>
+        <v>0.5075</v>
       </c>
       <c r="J27" t="n">
-        <v>11.5154</v>
+        <v>13.195</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0885</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.262</v>
+        <v>-2.301</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3632</v>
+        <v>-0.2443</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.443199999999999</v>
+        <v>-6.3518</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4565</v>
+        <v>-0.3016</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.869</v>
+        <v>-7.8416</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8195</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.307</v>
+        <v>-14.612</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>0.97</v>
       </c>
       <c r="I32" t="n">
-        <v>0.059</v>
+        <v>0.0108</v>
       </c>
       <c r="J32" t="n">
-        <v>1.239</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0199</v>
+        <v>-0.0496</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4179</v>
+        <v>-1.0416</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.78</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2704</v>
+        <v>-0.2204</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.6784</v>
+        <v>-4.6284</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.49</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7244</v>
+        <v>-0.4918</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.2124</v>
+        <v>-10.3278</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.32</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9329</v>
+        <v>-0.6504</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.5909</v>
+        <v>-13.6584</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.65</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3927</v>
+        <v>1.273</v>
       </c>
       <c r="J37" t="n">
-        <v>29.2467</v>
+        <v>26.733</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.58</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2565</v>
+        <v>1.1912</v>
       </c>
       <c r="J38" t="n">
-        <v>26.3865</v>
+        <v>25.0152</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.52</v>
       </c>
       <c r="I39" t="n">
-        <v>1.133</v>
+        <v>1.1205</v>
       </c>
       <c r="J39" t="n">
-        <v>23.793</v>
+        <v>23.5305</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7356</v>
+        <v>0.8551</v>
       </c>
       <c r="J40" t="n">
-        <v>15.4476</v>
+        <v>17.9571</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>1.21</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4204</v>
+        <v>0.5316</v>
       </c>
       <c r="J41" t="n">
-        <v>8.8284</v>
+        <v>11.1636</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.88</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7895</v>
+        <v>1.5284</v>
       </c>
       <c r="J42" t="n">
-        <v>34.0005</v>
+        <v>29.0396</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.55</v>
       </c>
       <c r="I43" t="n">
-        <v>1.173</v>
+        <v>1.1513</v>
       </c>
       <c r="J43" t="n">
-        <v>22.287</v>
+        <v>21.8747</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.4</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8267</v>
+        <v>0.9518</v>
       </c>
       <c r="J44" t="n">
-        <v>15.7073</v>
+        <v>18.0842</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8053</v>
+        <v>0.9322</v>
       </c>
       <c r="J45" t="n">
-        <v>15.3007</v>
+        <v>17.7118</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.3</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6107</v>
+        <v>0.7353</v>
       </c>
       <c r="J46" t="n">
-        <v>11.6033</v>
+        <v>13.9707</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>0.78</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2025</v>
+        <v>-0.184</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.8475</v>
+        <v>-3.496</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>0.65</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4032</v>
+        <v>-0.3221</v>
       </c>
       <c r="J48" t="n">
-        <v>-7.6608</v>
+        <v>-6.1199</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.59</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5029</v>
+        <v>-0.3791</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.555099999999999</v>
+        <v>-7.2029</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.59</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5029</v>
+        <v>-0.3791</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.555099999999999</v>
+        <v>-7.2029</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.26</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9851</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.7169</v>
+        <v>-13.129</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7252</v>
+        <v>0.8996</v>
       </c>
       <c r="J52" t="n">
-        <v>21.756</v>
+        <v>26.988</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.33</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5315</v>
+        <v>0.6392</v>
       </c>
       <c r="J53" t="n">
-        <v>15.945</v>
+        <v>19.176</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.97</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1225</v>
+        <v>-0.0584</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.675</v>
+        <v>-1.752</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3726</v>
+        <v>-0.2282</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.178</v>
+        <v>-6.846</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3869</v>
+        <v>-0.2383</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.607</v>
+        <v>-7.149</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.39</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6173</v>
+        <v>0.7507</v>
       </c>
       <c r="J57" t="n">
-        <v>18.519</v>
+        <v>22.521</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4639</v>
+        <v>0.5477</v>
       </c>
       <c r="J58" t="n">
-        <v>13.917</v>
+        <v>16.431</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.153</v>
+        <v>-0.081</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.59</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.95</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.153</v>
+        <v>-0.081</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.59</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5416</v>
+        <v>-0.3511</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.248</v>
+        <v>-10.533</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.01</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1002</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>3.006</v>
+        <v>2.085</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0055</v>
+        <v>-0.0214</v>
       </c>
       <c r="J63" t="n">
-        <v>0.165</v>
+        <v>-0.642</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.9</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.156</v>
+        <v>-0.1217</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.68</v>
+        <v>-3.651</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4495</v>
+        <v>-0.2915</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.485</v>
+        <v>-8.744999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4495</v>
+        <v>-0.2915</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.485</v>
+        <v>-8.744999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.64</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4976</v>
+        <v>1.3212</v>
       </c>
       <c r="J67" t="n">
-        <v>44.928</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7014</v>
+        <v>0.7033</v>
       </c>
       <c r="J68" t="n">
-        <v>21.042</v>
+        <v>21.099</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.13</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3276</v>
+        <v>0.3869</v>
       </c>
       <c r="J69" t="n">
-        <v>9.827999999999999</v>
+        <v>11.607</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0877</v>
+        <v>0.1548</v>
       </c>
       <c r="J70" t="n">
-        <v>2.631</v>
+        <v>4.644</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5537</v>
+        <v>-0.4859</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.611</v>
+        <v>-14.577</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>0.908</v>
+        <v>1.0953</v>
       </c>
       <c r="J72" t="n">
-        <v>24.516</v>
+        <v>29.5731</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2271</v>
+        <v>0.2459</v>
       </c>
       <c r="J73" t="n">
-        <v>6.1317</v>
+        <v>6.6393</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.77</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4265</v>
+        <v>-0.269</v>
       </c>
       <c r="J74" t="n">
-        <v>-11.5155</v>
+        <v>-7.263</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.76</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4404</v>
+        <v>-0.2788</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.8908</v>
+        <v>-7.5276</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.454</v>
+        <v>-0.2885</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.258</v>
+        <v>-7.7895</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.6</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4212</v>
+        <v>1.2704</v>
       </c>
       <c r="J77" t="n">
-        <v>38.3724</v>
+        <v>34.3008</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9329</v>
+        <v>0.9314</v>
       </c>
       <c r="J78" t="n">
-        <v>25.1883</v>
+        <v>25.1478</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.27</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7248</v>
+        <v>0.7262</v>
       </c>
       <c r="J79" t="n">
-        <v>19.5696</v>
+        <v>19.6074</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.528</v>
+        <v>-0.4585</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.256</v>
+        <v>-12.3795</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.85</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6057</v>
+        <v>-0.5412</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.3539</v>
+        <v>-14.6124</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1517</v>
+        <v>0.138</v>
       </c>
       <c r="J82" t="n">
-        <v>4.551</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.04</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1517</v>
+        <v>0.138</v>
       </c>
       <c r="J83" t="n">
-        <v>4.551</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2099</v>
+        <v>-0.1358</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.297</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2637</v>
+        <v>-0.1673</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.911</v>
+        <v>-5.019</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4611</v>
+        <v>-0.297</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.833</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.54</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7694</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>23.082</v>
+        <v>28.746</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.4</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6058</v>
+        <v>0.7409</v>
       </c>
       <c r="J88" t="n">
-        <v>18.174</v>
+        <v>22.227</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.154</v>
+        <v>-0.0761</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.62</v>
+        <v>-2.283</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1917</v>
+        <v>-0.1014</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.751</v>
+        <v>-3.042</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.422</v>
+        <v>-0.2626</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.66</v>
+        <v>-7.878</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.71</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4921</v>
+        <v>1.3377</v>
       </c>
       <c r="J92" t="n">
-        <v>28.3499</v>
+        <v>25.4163</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.6</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2819</v>
+        <v>1.2107</v>
       </c>
       <c r="J93" t="n">
-        <v>24.3561</v>
+        <v>23.0033</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.6</v>
       </c>
       <c r="I94" t="n">
-        <v>1.2819</v>
+        <v>1.2107</v>
       </c>
       <c r="J94" t="n">
-        <v>24.3561</v>
+        <v>23.0033</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.29</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5926</v>
+        <v>0.7149</v>
       </c>
       <c r="J95" t="n">
-        <v>11.2594</v>
+        <v>13.5831</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>1.26</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5258</v>
+        <v>0.6453</v>
       </c>
       <c r="J96" t="n">
-        <v>9.9902</v>
+        <v>12.2607</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>0.77</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.2561</v>
+        <v>-0.2175</v>
       </c>
       <c r="J97" t="n">
-        <v>-4.8659</v>
+        <v>-4.1325</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3827</v>
+        <v>-0.2984</v>
       </c>
       <c r="J98" t="n">
-        <v>-7.2713</v>
+        <v>-5.6696</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.59</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.5647</v>
+        <v>-0.3888</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.7293</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.59</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5647</v>
+        <v>-0.3888</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.7293</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5951</v>
+        <v>-0.4073</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.3069</v>
+        <v>-7.7387</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.07</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2304</v>
+        <v>0.2279</v>
       </c>
       <c r="J102" t="n">
-        <v>5.9904</v>
+        <v>5.9254</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.01</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1051</v>
+        <v>0.0737</v>
       </c>
       <c r="J103" t="n">
-        <v>2.7326</v>
+        <v>1.9162</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3398</v>
+        <v>-0.2217</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.8348</v>
+        <v>-5.7642</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3558</v>
+        <v>-0.2315</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.2508</v>
+        <v>-6.019</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5954</v>
+        <v>-0.3941</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.4804</v>
+        <v>-10.2466</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.45</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1125</v>
+        <v>1.0735</v>
       </c>
       <c r="J107" t="n">
-        <v>28.925</v>
+        <v>27.911</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0918</v>
+        <v>1.0604</v>
       </c>
       <c r="J108" t="n">
-        <v>28.3868</v>
+        <v>27.5704</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6039</v>
+        <v>0.6277</v>
       </c>
       <c r="J109" t="n">
-        <v>15.7014</v>
+        <v>16.3202</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2292</v>
+        <v>-0.1487</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.9592</v>
+        <v>-3.8662</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.98</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2292</v>
+        <v>-0.1487</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.9592</v>
+        <v>-3.8662</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3594</v>
+        <v>0.3953</v>
       </c>
       <c r="J112" t="n">
-        <v>8.984999999999999</v>
+        <v>9.8825</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0148</v>
+        <v>-0.035</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.37</v>
+        <v>-0.875</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1908</v>
+        <v>-0.1425</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.77</v>
+        <v>-3.5625</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.67</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5309</v>
+        <v>-0.3479</v>
       </c>
       <c r="J115" t="n">
-        <v>-13.2725</v>
+        <v>-8.6975</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5575</v>
+        <v>-0.3668</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.9375</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6176</v>
+        <v>1.4042</v>
       </c>
       <c r="J117" t="n">
-        <v>40.44</v>
+        <v>35.105</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5901</v>
+        <v>0.6635</v>
       </c>
       <c r="J118" t="n">
-        <v>14.7525</v>
+        <v>16.5875</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5644</v>
+        <v>0.6402</v>
       </c>
       <c r="J119" t="n">
-        <v>14.11</v>
+        <v>16.005</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.16</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3605</v>
+        <v>0.4441</v>
       </c>
       <c r="J120" t="n">
-        <v>9.012499999999999</v>
+        <v>11.1025</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.05</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0516</v>
+        <v>0.1315</v>
       </c>
       <c r="J121" t="n">
-        <v>1.29</v>
+        <v>3.2875</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.03</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1825</v>
+        <v>0.162</v>
       </c>
       <c r="J122" t="n">
-        <v>4.1975</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>0.77</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3524</v>
+        <v>-0.2422</v>
       </c>
       <c r="J123" t="n">
-        <v>-8.1052</v>
+        <v>-5.5706</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.77</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3524</v>
+        <v>-0.2422</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.1052</v>
+        <v>-5.5706</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4644</v>
+        <v>-0.3085</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.6812</v>
+        <v>-7.0955</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5221</v>
+        <v>-0.3463</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.0083</v>
+        <v>-7.9649</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.71</v>
       </c>
       <c r="I127" t="n">
-        <v>1.5715</v>
+        <v>1.3746</v>
       </c>
       <c r="J127" t="n">
-        <v>36.1445</v>
+        <v>31.6158</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.527</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>12.121</v>
+        <v>14.0852</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5022</v>
+        <v>0.5885</v>
       </c>
       <c r="J129" t="n">
-        <v>11.5506</v>
+        <v>13.5355</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4274</v>
+        <v>0.5151</v>
       </c>
       <c r="J130" t="n">
-        <v>9.8302</v>
+        <v>11.8473</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>1.19</v>
       </c>
       <c r="I131" t="n">
-        <v>0.4274</v>
+        <v>0.5151</v>
       </c>
       <c r="J131" t="n">
-        <v>9.8302</v>
+        <v>11.8473</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>0.76</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1775</v>
+        <v>-0.1642</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.55</v>
+        <v>-3.284</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>0.63</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3761</v>
+        <v>-0.3131</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.522</v>
+        <v>-6.262</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.43</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.7255</v>
+        <v>-0.507</v>
       </c>
       <c r="J134" t="n">
-        <v>-14.51</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.33</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.6052</v>
       </c>
       <c r="J135" t="n">
-        <v>-17.45</v>
+        <v>-12.104</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.28</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9403</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.806</v>
+        <v>-13.114</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>2.05</v>
       </c>
       <c r="I137" t="n">
-        <v>1.9814</v>
+        <v>1.691</v>
       </c>
       <c r="J137" t="n">
-        <v>39.628</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.9</v>
       </c>
       <c r="I138" t="n">
-        <v>1.7745</v>
+        <v>1.5284</v>
       </c>
       <c r="J138" t="n">
-        <v>35.49</v>
+        <v>30.568</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.61</v>
       </c>
       <c r="I139" t="n">
-        <v>1.2094</v>
+        <v>1.2097</v>
       </c>
       <c r="J139" t="n">
-        <v>24.188</v>
+        <v>24.194</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7619</v>
+        <v>0.9095</v>
       </c>
       <c r="J140" t="n">
-        <v>15.238</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>1.21</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3776</v>
+        <v>0.4985</v>
       </c>
       <c r="J141" t="n">
-        <v>7.552</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.88</v>
       </c>
       <c r="I142" t="n">
-        <v>1.9476</v>
+        <v>1.652</v>
       </c>
       <c r="J142" t="n">
-        <v>58.428</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2678</v>
+        <v>0.2952</v>
       </c>
       <c r="J143" t="n">
-        <v>8.034000000000001</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4153</v>
+        <v>-0.3491</v>
       </c>
       <c r="J144" t="n">
-        <v>-12.459</v>
+        <v>-10.473</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.472</v>
+        <v>-0.4071</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.16</v>
+        <v>-12.213</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.75</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8217</v>
+        <v>-0.7783</v>
       </c>
       <c r="J146" t="n">
-        <v>-24.651</v>
+        <v>-23.349</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6781</v>
+        <v>0.8336</v>
       </c>
       <c r="J147" t="n">
-        <v>20.343</v>
+        <v>25.008</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6301</v>
+        <v>0.768</v>
       </c>
       <c r="J148" t="n">
-        <v>18.903</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0578</v>
+        <v>0.0857</v>
       </c>
       <c r="J149" t="n">
-        <v>1.734</v>
+        <v>2.571</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.394</v>
+        <v>-0.2445</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.82</v>
+        <v>-7.335</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.4611</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.64</v>
+        <v>-13.833</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.25</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.7738</v>
       </c>
       <c r="J152" t="n">
-        <v>13.3848</v>
+        <v>17.0236</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.75</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2852</v>
+        <v>-0.2374</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.2744</v>
+        <v>-5.2228</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.46</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.7468</v>
+        <v>-0.5098</v>
       </c>
       <c r="J154" t="n">
-        <v>-16.4296</v>
+        <v>-11.2156</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.4</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.8244</v>
+        <v>-0.5666</v>
       </c>
       <c r="J155" t="n">
-        <v>-18.1368</v>
+        <v>-12.4652</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.33</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9112</v>
+        <v>-0.633</v>
       </c>
       <c r="J156" t="n">
-        <v>-20.0464</v>
+        <v>-13.926</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4134</v>
+        <v>1.2853</v>
       </c>
       <c r="J157" t="n">
-        <v>31.0948</v>
+        <v>28.2766</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.6</v>
       </c>
       <c r="I158" t="n">
-        <v>1.298</v>
+        <v>1.2152</v>
       </c>
       <c r="J158" t="n">
-        <v>28.556</v>
+        <v>26.7344</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.46</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9961</v>
+        <v>1.0499</v>
       </c>
       <c r="J159" t="n">
-        <v>21.9142</v>
+        <v>23.0978</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.31</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6488</v>
+        <v>0.7671</v>
       </c>
       <c r="J160" t="n">
-        <v>14.2736</v>
+        <v>16.8762</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>1.26</v>
       </c>
       <c r="I161" t="n">
-        <v>0.5367</v>
+        <v>0.6522</v>
       </c>
       <c r="J161" t="n">
-        <v>11.8074</v>
+        <v>14.3484</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>0.97</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1428</v>
+        <v>0.1442</v>
       </c>
       <c r="J162" t="n">
-        <v>2.5704</v>
+        <v>2.5956</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.52</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.6178</v>
+        <v>-0.4359</v>
       </c>
       <c r="J163" t="n">
-        <v>-11.1204</v>
+        <v>-7.8462</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.51</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.6347</v>
+        <v>-0.445</v>
       </c>
       <c r="J164" t="n">
-        <v>-11.4246</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.37</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.8381</v>
+        <v>-0.5785</v>
       </c>
       <c r="J165" t="n">
-        <v>-15.0858</v>
+        <v>-10.413</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8515</v>
+        <v>-0.5883</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.327</v>
+        <v>-10.5894</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.95</v>
       </c>
       <c r="I167" t="n">
-        <v>1.8714</v>
+        <v>1.5896</v>
       </c>
       <c r="J167" t="n">
-        <v>33.6852</v>
+        <v>28.6128</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.75</v>
       </c>
       <c r="I168" t="n">
-        <v>1.5236</v>
+        <v>1.3686</v>
       </c>
       <c r="J168" t="n">
-        <v>27.4248</v>
+        <v>24.6348</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.64</v>
       </c>
       <c r="I169" t="n">
-        <v>1.3113</v>
+        <v>1.2454</v>
       </c>
       <c r="J169" t="n">
-        <v>23.6034</v>
+        <v>22.4172</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.41</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8151</v>
+        <v>0.9563</v>
       </c>
       <c r="J170" t="n">
-        <v>14.6718</v>
+        <v>17.2134</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>1.21</v>
       </c>
       <c r="I171" t="n">
-        <v>0.3865</v>
+        <v>0.5059</v>
       </c>
       <c r="J171" t="n">
-        <v>6.957</v>
+        <v>9.106199999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4702/event_4702_evp_summary.xlsx
+++ b/database/event/4702/event_4702_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5395</v>
+        <v>4.2137</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0241</v>
+        <v>0.9506</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4113</v>
+        <v>1.294</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5395</v>
+        <v>4.2137</v>
       </c>
       <c r="F2" t="n">
-        <v>3.56</v>
+        <v>3.2681</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9795</v>
+        <v>0.9456</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4574</v>
+        <v>4.4279</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6407</v>
+        <v>4.542</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9795</v>
+        <v>0.9456</v>
       </c>
       <c r="K2" t="n">
         <v>113</v>
@@ -529,7 +529,7 @@
         <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6202</v>
+        <v>5.4876</v>
       </c>
       <c r="N2" t="n">
         <v>177</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6624</v>
+        <v>3.3615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8262</v>
+        <v>0.7584</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0154</v>
+        <v>0.906</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6624</v>
+        <v>3.3615</v>
       </c>
       <c r="F3" t="n">
-        <v>3.011</v>
+        <v>2.7523</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6514</v>
+        <v>0.6092</v>
       </c>
       <c r="H3" t="n">
-        <v>3.252</v>
+        <v>3.2989</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3857</v>
+        <v>3.3839</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6514</v>
+        <v>0.6092</v>
       </c>
       <c r="K3" t="n">
         <v>113</v>
@@ -575,7 +575,7 @@
         <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>4.0371</v>
+        <v>3.9931</v>
       </c>
       <c r="N3" t="n">
         <v>177</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4667</v>
+        <v>3.3536</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7821</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.927</v>
+        <v>0.9024</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4667</v>
+        <v>3.3536</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4432</v>
+        <v>2.3405</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0235</v>
+        <v>1.0131</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4432</v>
+        <v>2.3977</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5437</v>
+        <v>2.4595</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0235</v>
+        <v>1.0131</v>
       </c>
       <c r="K4" t="n">
         <v>113</v>
@@ -621,7 +621,7 @@
         <v>64</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5672</v>
+        <v>3.4726</v>
       </c>
       <c r="N4" t="n">
         <v>177</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3191</v>
+        <v>3.0009</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7488</v>
+        <v>0.677</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.7419</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3191</v>
+        <v>3.0009</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3191</v>
+        <v>3.0009</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9283</v>
+        <v>3.843</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9283</v>
+        <v>3.843</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9283</v>
+        <v>3.843</v>
       </c>
       <c r="N5" t="n">
         <v>124</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2993</v>
+        <v>2.9675</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7443</v>
+        <v>0.6695</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8515</v>
+        <v>0.7267</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2993</v>
+        <v>2.9675</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2993</v>
+        <v>2.9675</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.885</v>
+        <v>3.7699</v>
       </c>
       <c r="I6" t="n">
-        <v>3.885</v>
+        <v>3.7699</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.885</v>
+        <v>3.7699</v>
       </c>
       <c r="N6" t="n">
         <v>141</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8928</v>
+        <v>2.5838</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6526</v>
+        <v>0.5829</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6679</v>
+        <v>0.552</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8928</v>
+        <v>2.5838</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8928</v>
+        <v>2.5838</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9924</v>
+        <v>2.9301</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9924</v>
+        <v>2.9301</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9924</v>
+        <v>2.9301</v>
       </c>
       <c r="N7" t="n">
         <v>124</v>
@@ -768,231 +768,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8159</v>
+        <v>2.5293</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6353</v>
+        <v>0.5706</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6332</v>
+        <v>0.5272</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8159</v>
+        <v>2.5293</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8159</v>
+        <v>2.3207</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.2086</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8236</v>
+        <v>2.3543</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8236</v>
+        <v>2.415</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2086</v>
       </c>
       <c r="K8" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8236</v>
+        <v>2.6236</v>
       </c>
       <c r="N8" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5751</v>
+        <v>2.5064</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5809</v>
+        <v>0.5654</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5245</v>
+        <v>0.5168</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5751</v>
+        <v>2.5064</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5751</v>
+        <v>2.5064</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5751</v>
+        <v>2.7607</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5751</v>
+        <v>2.7607</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5751</v>
+        <v>2.7607</v>
       </c>
       <c r="N9" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5642</v>
+        <v>2.3749</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5785</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5196</v>
+        <v>0.4569</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5642</v>
+        <v>2.3749</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3562</v>
+        <v>2.3749</v>
       </c>
       <c r="G10" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3562</v>
+        <v>2.4729</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4531</v>
+        <v>2.4729</v>
       </c>
       <c r="J10" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6611</v>
+        <v>2.4729</v>
       </c>
       <c r="N10" t="n">
-        <v>177</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3314</v>
+        <v>2.2219</v>
       </c>
       <c r="C11" t="n">
-        <v>0.526</v>
+        <v>0.5013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4145</v>
+        <v>0.3873</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3314</v>
+        <v>2.2219</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8694</v>
+        <v>2.2219</v>
       </c>
       <c r="G11" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8694</v>
+        <v>2.2219</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8694</v>
+        <v>2.2219</v>
       </c>
       <c r="J11" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="L11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3314</v>
+        <v>2.2219</v>
       </c>
       <c r="N11" t="n">
-        <v>181</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2718</v>
+        <v>2.1427</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5125</v>
+        <v>0.4834</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3876</v>
+        <v>0.3512</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2718</v>
+        <v>2.1427</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2718</v>
+        <v>1.7383</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.4044</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2718</v>
+        <v>1.7383</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2718</v>
+        <v>1.7383</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.4044</v>
       </c>
       <c r="K12" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2718</v>
+        <v>2.1427</v>
       </c>
       <c r="N12" t="n">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2113</v>
+        <v>1.8642</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4989</v>
+        <v>0.4206</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3603</v>
+        <v>0.2244</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2113</v>
+        <v>1.8642</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9507</v>
+        <v>2.6237</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7595</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1194</v>
+        <v>3.0175</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1194</v>
+        <v>3.0175</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7595</v>
       </c>
       <c r="K13" t="n">
         <v>117</v>
@@ -1035,7 +1035,7 @@
         <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>2.38</v>
+        <v>2.258</v>
       </c>
       <c r="N13" t="n">
         <v>181</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7911</v>
+        <v>1.7953</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4041</v>
+        <v>0.405</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1706</v>
+        <v>0.1931</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7911</v>
+        <v>1.7953</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7911</v>
+        <v>1.7953</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7911</v>
+        <v>1.7953</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7911</v>
+        <v>1.7953</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7911</v>
+        <v>1.7953</v>
       </c>
       <c r="N14" t="n">
         <v>124</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.71</v>
+        <v>1.7157</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3858</v>
+        <v>0.3871</v>
       </c>
       <c r="D15" t="n">
-        <v>0.134</v>
+        <v>0.1568</v>
       </c>
       <c r="E15" t="n">
-        <v>1.71</v>
+        <v>1.7157</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6326</v>
+        <v>1.6339</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0774</v>
+        <v>0.0818</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6326</v>
+        <v>1.6339</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6997</v>
+        <v>1.676</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0774</v>
+        <v>0.0818</v>
       </c>
       <c r="K15" t="n">
         <v>113</v>
@@ -1127,7 +1127,7 @@
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7771</v>
+        <v>1.7578</v>
       </c>
       <c r="N15" t="n">
         <v>177</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3763</v>
+        <v>1.2996</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3105</v>
+        <v>0.2932</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0167</v>
+        <v>-0.0326</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3763</v>
+        <v>1.2996</v>
       </c>
       <c r="F16" t="n">
-        <v>0.834</v>
+        <v>0.8021</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5423</v>
+        <v>0.4975</v>
       </c>
       <c r="H16" t="n">
-        <v>0.834</v>
+        <v>0.8021</v>
       </c>
       <c r="I16" t="n">
-        <v>0.834</v>
+        <v>0.8021</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5423</v>
+        <v>0.4975</v>
       </c>
       <c r="K16" t="n">
         <v>117</v>
@@ -1173,7 +1173,7 @@
         <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3763</v>
+        <v>1.2996</v>
       </c>
       <c r="N16" t="n">
         <v>181</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2326</v>
+        <v>1.141</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2781</v>
+        <v>0.2574</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1048</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2326</v>
+        <v>1.141</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2326</v>
+        <v>1.141</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2326</v>
+        <v>1.141</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2326</v>
+        <v>1.141</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2326</v>
+        <v>1.141</v>
       </c>
       <c r="N17" t="n">
         <v>116</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.184</v>
+        <v>1.1218</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2671</v>
+        <v>0.2531</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1035</v>
+        <v>-0.1135</v>
       </c>
       <c r="E18" t="n">
-        <v>1.184</v>
+        <v>1.1218</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.899</v>
       </c>
       <c r="G18" t="n">
-        <v>0.246</v>
+        <v>0.2228</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.899</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.899</v>
       </c>
       <c r="J18" t="n">
-        <v>0.246</v>
+        <v>0.2228</v>
       </c>
       <c r="K18" t="n">
         <v>117</v>
@@ -1265,7 +1265,7 @@
         <v>64</v>
       </c>
       <c r="M18" t="n">
-        <v>1.184</v>
+        <v>1.1218</v>
       </c>
       <c r="N18" t="n">
         <v>181</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1535</v>
+        <v>1.0116</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2602</v>
+        <v>0.2282</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1173</v>
+        <v>-0.1637</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1535</v>
+        <v>1.0116</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3532</v>
+        <v>1.2366</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1997</v>
+        <v>-0.225</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3532</v>
+        <v>1.2366</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3532</v>
+        <v>1.2366</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1997</v>
+        <v>-0.225</v>
       </c>
       <c r="K19" t="n">
         <v>117</v>
@@ -1311,7 +1311,7 @@
         <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1535</v>
+        <v>1.0116</v>
       </c>
       <c r="N19" t="n">
         <v>181</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0195</v>
+        <v>0.8956</v>
       </c>
       <c r="C20" t="n">
-        <v>0.23</v>
+        <v>0.202</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1778</v>
+        <v>-0.2165</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0195</v>
+        <v>0.8956</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0195</v>
+        <v>0.8956</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0195</v>
+        <v>0.8956</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0195</v>
+        <v>0.8956</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0195</v>
+        <v>0.8956</v>
       </c>
       <c r="N20" t="n">
         <v>116</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0087</v>
+        <v>0.8845</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2276</v>
+        <v>0.1995</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1826</v>
+        <v>-0.2216</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0087</v>
+        <v>0.8845</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0087</v>
+        <v>0.8845</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0087</v>
+        <v>0.8845</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0087</v>
+        <v>0.8845</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0087</v>
+        <v>0.8845</v>
       </c>
       <c r="N21" t="n">
         <v>116</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="C22" t="n">
-        <v>0.157</v>
+        <v>0.1384</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3238</v>
+        <v>-0.3449</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.179</v>
+        <v>-0.2305</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0404</v>
+        <v>-0.052</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7188</v>
+        <v>-0.7291</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.179</v>
+        <v>-0.2305</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.179</v>
+        <v>-0.2305</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.179</v>
+        <v>-0.2305</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.179</v>
+        <v>-0.2305</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.179</v>
+        <v>-0.2305</v>
       </c>
       <c r="N23" t="n">
         <v>116</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2381</v>
+        <v>-0.2403</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0537</v>
+        <v>-0.0542</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7336</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2381</v>
+        <v>-0.2403</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2381</v>
+        <v>-0.2403</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2381</v>
+        <v>-0.2403</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2381</v>
+        <v>-0.2403</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2381</v>
+        <v>-0.2403</v>
       </c>
       <c r="N24" t="n">
         <v>141</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3329</v>
+        <v>-0.3539</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0751</v>
+        <v>-0.0798</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7883</v>
+        <v>-0.7853</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3329</v>
+        <v>-0.3539</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3329</v>
+        <v>-0.3539</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3329</v>
+        <v>-0.3539</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3329</v>
+        <v>-0.3539</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3329</v>
+        <v>-0.3539</v>
       </c>
       <c r="N25" t="n">
         <v>141</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6693</v>
+        <v>-0.7748</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.151</v>
+        <v>-0.1748</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9402</v>
+        <v>-0.9769</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6693</v>
+        <v>-0.7748</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6693</v>
+        <v>-0.7748</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6693</v>
+        <v>-0.7748</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6693</v>
+        <v>-0.7748</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6693</v>
+        <v>-0.7748</v>
       </c>
       <c r="N26" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8171</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1843</v>
+        <v>-0.1814</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0069</v>
+        <v>-0.9902</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8171</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8171</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8171</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8171</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8171</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.2101</v>
+        <v>-1.3035</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.273</v>
+        <v>-0.2941</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1843</v>
+        <v>-1.2176</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2101</v>
+        <v>-1.3035</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.2101</v>
+        <v>-1.3035</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.2101</v>
+        <v>-1.3035</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.2101</v>
+        <v>-1.3035</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.2101</v>
+        <v>-1.3035</v>
       </c>
       <c r="N28" t="n">
         <v>121</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.3543</v>
+        <v>-1.4243</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3055</v>
+        <v>-0.3213</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2494</v>
+        <v>-1.2726</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3543</v>
+        <v>-1.4243</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.3543</v>
+        <v>-1.4243</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.3543</v>
+        <v>-1.4243</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.3543</v>
+        <v>-1.4243</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.3543</v>
+        <v>-1.4243</v>
       </c>
       <c r="N29" t="n">
         <v>121</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.4603</v>
+        <v>-1.4864</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3294</v>
+        <v>-0.3353</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2973</v>
+        <v>-1.3008</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.4603</v>
+        <v>-1.4864</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4603</v>
+        <v>-1.4864</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4603</v>
+        <v>-1.4864</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4603</v>
+        <v>-1.4864</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4603</v>
+        <v>-1.4864</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.6602</v>
+        <v>-1.7413</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3745</v>
+        <v>-0.3928</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3875</v>
+        <v>-1.4169</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.6602</v>
+        <v>-1.7413</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.6602</v>
+        <v>-1.7413</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.6602</v>
+        <v>-1.7413</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.6602</v>
+        <v>-1.7413</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.6602</v>
+        <v>-1.7413</v>
       </c>
       <c r="N31" t="n">
         <v>121</v>
@@ -1969,10 +1969,10 @@
         <v>1.26</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7078</v>
       </c>
       <c r="J2" t="n">
-        <v>27.126</v>
+        <v>25.4808</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1871</v>
+        <v>0.1934</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7356</v>
+        <v>6.9624</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1041</v>
+        <v>-0.1066</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.7476</v>
+        <v>-3.8376</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.97</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.141</v>
+        <v>-0.143</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.076</v>
+        <v>-5.148</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1758</v>
+        <v>-0.1766</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.3288</v>
+        <v>-6.3576</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8885</v>
+        <v>0.841</v>
       </c>
       <c r="J7" t="n">
-        <v>31.986</v>
+        <v>30.276</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.95</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0757</v>
+        <v>-0.0859</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7252</v>
+        <v>-3.0924</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1228</v>
+        <v>-0.1353</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.4208</v>
+        <v>-4.8708</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1559</v>
+        <v>-0.1691</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.6124</v>
+        <v>-6.0876</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2488</v>
+        <v>-0.2621</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.956799999999999</v>
+        <v>-9.435600000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.49</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1276</v>
+        <v>1.1197</v>
       </c>
       <c r="J12" t="n">
-        <v>31.5728</v>
+        <v>31.3516</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7924</v>
+        <v>0.7522</v>
       </c>
       <c r="J13" t="n">
-        <v>22.1872</v>
+        <v>21.0616</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7924</v>
+        <v>0.7522</v>
       </c>
       <c r="J14" t="n">
-        <v>22.1872</v>
+        <v>21.0616</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3838</v>
+        <v>0.3852</v>
       </c>
       <c r="J15" t="n">
-        <v>10.7464</v>
+        <v>10.7856</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6761</v>
+        <v>-0.626</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.9308</v>
+        <v>-17.528</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6651</v>
+        <v>0.6328</v>
       </c>
       <c r="J17" t="n">
-        <v>18.6228</v>
+        <v>17.7184</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4019</v>
+        <v>0.3919</v>
       </c>
       <c r="J18" t="n">
-        <v>11.2532</v>
+        <v>10.9732</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.124</v>
+        <v>-0.1391</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.472</v>
+        <v>-3.8948</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4265</v>
+        <v>-0.4366</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.942</v>
+        <v>-12.2248</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4906</v>
+        <v>-0.4974</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.7368</v>
+        <v>-13.9272</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.68</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3367</v>
+        <v>1.3176</v>
       </c>
       <c r="J22" t="n">
-        <v>34.7542</v>
+        <v>34.2576</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.59</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2278</v>
+        <v>1.2016</v>
       </c>
       <c r="J23" t="n">
-        <v>31.9228</v>
+        <v>31.2416</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8998</v>
+        <v>0.8516</v>
       </c>
       <c r="J24" t="n">
-        <v>23.3948</v>
+        <v>22.1416</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.463</v>
+        <v>0.4626</v>
       </c>
       <c r="J25" t="n">
-        <v>12.038</v>
+        <v>12.0276</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7516</v>
+        <v>-0.6887</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.5416</v>
+        <v>-17.9062</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5075</v>
+        <v>0.4809</v>
       </c>
       <c r="J27" t="n">
-        <v>13.195</v>
+        <v>12.5034</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0885</v>
+        <v>-0.1059</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.301</v>
+        <v>-2.7534</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2443</v>
+        <v>-0.2627</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.3518</v>
+        <v>-6.8302</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3016</v>
+        <v>-0.3188</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.8416</v>
+        <v>-8.2888</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.612</v>
+        <v>-14.716</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>0.97</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0108</v>
+        <v>-0.0146</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2268</v>
+        <v>-0.3066</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0496</v>
+        <v>-0.0723</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.0416</v>
+        <v>-1.5183</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.78</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2204</v>
+        <v>-0.2423</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.6284</v>
+        <v>-5.0883</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.49</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4918</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.3278</v>
+        <v>-10.5525</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.32</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6504</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.6584</v>
+        <v>-13.6437</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.65</v>
       </c>
       <c r="I37" t="n">
-        <v>1.273</v>
+        <v>1.2551</v>
       </c>
       <c r="J37" t="n">
-        <v>26.733</v>
+        <v>26.3571</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.58</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1912</v>
+        <v>1.1672</v>
       </c>
       <c r="J38" t="n">
-        <v>25.0152</v>
+        <v>24.5112</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.52</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1205</v>
+        <v>1.0909</v>
       </c>
       <c r="J39" t="n">
-        <v>23.5305</v>
+        <v>22.9089</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8551</v>
+        <v>0.8168</v>
       </c>
       <c r="J40" t="n">
-        <v>17.9571</v>
+        <v>17.1528</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>1.21</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5316</v>
+        <v>0.5305</v>
       </c>
       <c r="J41" t="n">
-        <v>11.1636</v>
+        <v>11.1405</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.88</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5284</v>
+        <v>1.5272</v>
       </c>
       <c r="J42" t="n">
-        <v>29.0396</v>
+        <v>29.0168</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.55</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1513</v>
+        <v>1.1252</v>
       </c>
       <c r="J43" t="n">
-        <v>21.8747</v>
+        <v>21.3788</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.4</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9518</v>
+        <v>0.9055</v>
       </c>
       <c r="J44" t="n">
-        <v>18.0842</v>
+        <v>17.2045</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9322</v>
+        <v>0.887</v>
       </c>
       <c r="J45" t="n">
-        <v>17.7118</v>
+        <v>16.853</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.3</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7353</v>
+        <v>0.713</v>
       </c>
       <c r="J46" t="n">
-        <v>13.9707</v>
+        <v>13.547</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>0.78</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.184</v>
+        <v>-0.2139</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.496</v>
+        <v>-4.0641</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>0.65</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3221</v>
+        <v>-0.3456</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.1199</v>
+        <v>-6.5664</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.59</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3791</v>
+        <v>-0.3998</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.2029</v>
+        <v>-7.5962</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.59</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3791</v>
+        <v>-0.3998</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.2029</v>
+        <v>-7.5962</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.26</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6889</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.129</v>
+        <v>-13.0891</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8996</v>
+        <v>0.8566</v>
       </c>
       <c r="J52" t="n">
-        <v>26.988</v>
+        <v>25.698</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.33</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6392</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>19.176</v>
+        <v>18.675</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.97</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0584</v>
+        <v>-0.0646</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.752</v>
+        <v>-1.938</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2282</v>
+        <v>-0.2397</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.846</v>
+        <v>-7.191</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2383</v>
+        <v>-0.2498</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.149</v>
+        <v>-7.494</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.39</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7507</v>
+        <v>0.7212</v>
       </c>
       <c r="J57" t="n">
-        <v>22.521</v>
+        <v>21.636</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5477</v>
+        <v>0.5372</v>
       </c>
       <c r="J58" t="n">
-        <v>16.431</v>
+        <v>16.116</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.081</v>
+        <v>-0.09</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.43</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.95</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.081</v>
+        <v>-0.09</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.43</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3511</v>
+        <v>-0.3611</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.533</v>
+        <v>-10.833</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.01</v>
       </c>
       <c r="I62" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0663</v>
       </c>
       <c r="J62" t="n">
-        <v>2.085</v>
+        <v>1.989</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0214</v>
+        <v>-0.0315</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.642</v>
+        <v>-0.945</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.9</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1217</v>
+        <v>-0.1374</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.651</v>
+        <v>-4.122</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2915</v>
+        <v>-0.3072</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.744999999999999</v>
+        <v>-9.215999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2915</v>
+        <v>-0.3072</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.744999999999999</v>
+        <v>-9.215999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.64</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3212</v>
+        <v>1.2953</v>
       </c>
       <c r="J67" t="n">
-        <v>39.636</v>
+        <v>38.859</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7033</v>
+        <v>0.6728</v>
       </c>
       <c r="J68" t="n">
-        <v>21.099</v>
+        <v>20.184</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.13</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3869</v>
+        <v>0.3873</v>
       </c>
       <c r="J69" t="n">
-        <v>11.607</v>
+        <v>11.619</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1548</v>
+        <v>0.1712</v>
       </c>
       <c r="J70" t="n">
-        <v>4.644</v>
+        <v>5.136</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4859</v>
+        <v>-0.456</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.577</v>
+        <v>-13.68</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0953</v>
+        <v>1.0613</v>
       </c>
       <c r="J72" t="n">
-        <v>29.5731</v>
+        <v>28.6551</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2459</v>
+        <v>0.2521</v>
       </c>
       <c r="J73" t="n">
-        <v>6.6393</v>
+        <v>6.8067</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.77</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.269</v>
+        <v>-0.282</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.263</v>
+        <v>-7.614</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.76</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2788</v>
+        <v>-0.2916</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.5276</v>
+        <v>-7.8732</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2885</v>
+        <v>-0.3011</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.7895</v>
+        <v>-8.1297</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.6</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2704</v>
+        <v>1.2416</v>
       </c>
       <c r="J77" t="n">
-        <v>34.3008</v>
+        <v>33.5232</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9314</v>
+        <v>0.8743</v>
       </c>
       <c r="J78" t="n">
-        <v>25.1478</v>
+        <v>23.6061</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.27</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7262</v>
+        <v>0.6932</v>
       </c>
       <c r="J79" t="n">
-        <v>19.6074</v>
+        <v>18.7164</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4585</v>
+        <v>-0.4309</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.3795</v>
+        <v>-11.6343</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.85</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5412</v>
+        <v>-0.5058</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.6124</v>
+        <v>-13.6566</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>0.138</v>
+        <v>0.1404</v>
       </c>
       <c r="J82" t="n">
-        <v>4.14</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.04</v>
       </c>
       <c r="I83" t="n">
-        <v>0.138</v>
+        <v>0.1404</v>
       </c>
       <c r="J83" t="n">
-        <v>4.14</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1358</v>
+        <v>-0.1509</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.074</v>
+        <v>-4.527</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1673</v>
+        <v>-0.1831</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.019</v>
+        <v>-5.493</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.297</v>
+        <v>-0.3115</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.91</v>
+        <v>-9.345000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.54</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9143</v>
       </c>
       <c r="J87" t="n">
-        <v>28.746</v>
+        <v>27.429</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.4</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7409</v>
+        <v>0.7167</v>
       </c>
       <c r="J88" t="n">
-        <v>22.227</v>
+        <v>21.501</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0761</v>
+        <v>-0.0825</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.283</v>
+        <v>-2.475</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1014</v>
+        <v>-0.1093</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.042</v>
+        <v>-3.279</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2626</v>
+        <v>-0.273</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.878</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.71</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3377</v>
+        <v>1.3249</v>
       </c>
       <c r="J92" t="n">
-        <v>25.4163</v>
+        <v>25.1731</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.6</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2107</v>
+        <v>1.189</v>
       </c>
       <c r="J93" t="n">
-        <v>23.0033</v>
+        <v>22.591</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.6</v>
       </c>
       <c r="I94" t="n">
-        <v>1.2107</v>
+        <v>1.189</v>
       </c>
       <c r="J94" t="n">
-        <v>23.0033</v>
+        <v>22.591</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.29</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7149</v>
+        <v>0.6945</v>
       </c>
       <c r="J95" t="n">
-        <v>13.5831</v>
+        <v>13.1955</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>1.26</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6453</v>
+        <v>0.633</v>
       </c>
       <c r="J96" t="n">
-        <v>12.2607</v>
+        <v>12.027</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>0.77</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.2175</v>
+        <v>-0.2421</v>
       </c>
       <c r="J97" t="n">
-        <v>-4.1325</v>
+        <v>-4.5999</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2984</v>
+        <v>-0.3201</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.6696</v>
+        <v>-6.0819</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.59</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3888</v>
+        <v>-0.4071</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.3872</v>
+        <v>-7.7349</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.59</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3888</v>
+        <v>-0.4071</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.3872</v>
+        <v>-7.7349</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4073</v>
+        <v>-0.4246</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.7387</v>
+        <v>-8.067399999999999</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.07</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2279</v>
+        <v>0.2239</v>
       </c>
       <c r="J102" t="n">
-        <v>5.9254</v>
+        <v>5.8214</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.01</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0737</v>
+        <v>0.0694</v>
       </c>
       <c r="J103" t="n">
-        <v>1.9162</v>
+        <v>1.8044</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2217</v>
+        <v>-0.2389</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.7642</v>
+        <v>-6.2114</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2315</v>
+        <v>-0.2487</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.019</v>
+        <v>-6.4662</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3941</v>
+        <v>-0.4064</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.2466</v>
+        <v>-10.5664</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.45</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0735</v>
+        <v>1.0293</v>
       </c>
       <c r="J107" t="n">
-        <v>27.911</v>
+        <v>26.7618</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0604</v>
+        <v>1.0137</v>
       </c>
       <c r="J108" t="n">
-        <v>27.5704</v>
+        <v>26.3562</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6277</v>
+        <v>0.6066</v>
       </c>
       <c r="J109" t="n">
-        <v>16.3202</v>
+        <v>15.7716</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1487</v>
+        <v>-0.1377</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.8662</v>
+        <v>-3.5802</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.98</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1487</v>
+        <v>-0.1377</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.8662</v>
+        <v>-3.5802</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3953</v>
+        <v>0.3831</v>
       </c>
       <c r="J112" t="n">
-        <v>9.8825</v>
+        <v>9.577500000000001</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.035</v>
+        <v>-0.0467</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.875</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1425</v>
+        <v>-0.1588</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.5625</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.67</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3479</v>
+        <v>-0.362</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.6975</v>
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3668</v>
+        <v>-0.3801</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.17</v>
+        <v>-9.5025</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4042</v>
+        <v>1.3878</v>
       </c>
       <c r="J117" t="n">
-        <v>35.105</v>
+        <v>34.695</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6635</v>
+        <v>0.6409</v>
       </c>
       <c r="J118" t="n">
-        <v>16.5875</v>
+        <v>16.0225</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6402</v>
+        <v>0.6202</v>
       </c>
       <c r="J119" t="n">
-        <v>16.005</v>
+        <v>15.505</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.16</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4441</v>
+        <v>0.444</v>
       </c>
       <c r="J120" t="n">
-        <v>11.1025</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.05</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1315</v>
+        <v>0.155</v>
       </c>
       <c r="J121" t="n">
-        <v>3.2875</v>
+        <v>3.875</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.03</v>
       </c>
       <c r="I122" t="n">
-        <v>0.162</v>
+        <v>0.1512</v>
       </c>
       <c r="J122" t="n">
-        <v>3.726</v>
+        <v>3.4776</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>0.77</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2422</v>
+        <v>-0.2612</v>
       </c>
       <c r="J123" t="n">
-        <v>-5.5706</v>
+        <v>-6.0076</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.77</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2422</v>
+        <v>-0.2612</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.5706</v>
+        <v>-6.0076</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3085</v>
+        <v>-0.326</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.0955</v>
+        <v>-7.498</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3463</v>
+        <v>-0.3625</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.9649</v>
+        <v>-8.3375</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.71</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3746</v>
+        <v>1.3574</v>
       </c>
       <c r="J127" t="n">
-        <v>31.6158</v>
+        <v>31.2202</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5962</v>
       </c>
       <c r="J128" t="n">
-        <v>14.0852</v>
+        <v>13.7126</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5885</v>
+        <v>0.5749</v>
       </c>
       <c r="J129" t="n">
-        <v>13.5355</v>
+        <v>13.2227</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5151</v>
+        <v>0.5091</v>
       </c>
       <c r="J130" t="n">
-        <v>11.8473</v>
+        <v>11.7093</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>1.19</v>
       </c>
       <c r="I131" t="n">
-        <v>0.5151</v>
+        <v>0.5091</v>
       </c>
       <c r="J131" t="n">
-        <v>11.8473</v>
+        <v>11.7093</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>0.76</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1642</v>
+        <v>-0.202</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.284</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>0.63</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3131</v>
+        <v>-0.3419</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.262</v>
+        <v>-6.838</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.43</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.507</v>
+        <v>-0.5228</v>
       </c>
       <c r="J134" t="n">
-        <v>-10.14</v>
+        <v>-10.456</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.33</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6052</v>
+        <v>-0.6127</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.104</v>
+        <v>-12.254</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.28</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.6586</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.114</v>
+        <v>-13.172</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>2.05</v>
       </c>
       <c r="I137" t="n">
-        <v>1.691</v>
+        <v>1.7018</v>
       </c>
       <c r="J137" t="n">
-        <v>33.82</v>
+        <v>34.036</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.9</v>
       </c>
       <c r="I138" t="n">
-        <v>1.5284</v>
+        <v>1.531</v>
       </c>
       <c r="J138" t="n">
-        <v>30.568</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.61</v>
       </c>
       <c r="I139" t="n">
-        <v>1.2097</v>
+        <v>1.1907</v>
       </c>
       <c r="J139" t="n">
-        <v>24.194</v>
+        <v>23.814</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
-        <v>0.9095</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>18.19</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>1.21</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4985</v>
+        <v>0.5073</v>
       </c>
       <c r="J141" t="n">
-        <v>9.970000000000001</v>
+        <v>10.146</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.88</v>
       </c>
       <c r="I142" t="n">
-        <v>1.652</v>
+        <v>1.6371</v>
       </c>
       <c r="J142" t="n">
-        <v>49.56</v>
+        <v>49.113</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2952</v>
+        <v>0.2983</v>
       </c>
       <c r="J143" t="n">
-        <v>8.856</v>
+        <v>8.949</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3491</v>
+        <v>-0.3355</v>
       </c>
       <c r="J144" t="n">
-        <v>-10.473</v>
+        <v>-10.065</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4071</v>
+        <v>-0.3889</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.213</v>
+        <v>-11.667</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.75</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7783</v>
+        <v>-0.7208</v>
       </c>
       <c r="J146" t="n">
-        <v>-23.349</v>
+        <v>-21.624</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8336</v>
+        <v>0.7954</v>
       </c>
       <c r="J147" t="n">
-        <v>25.008</v>
+        <v>23.862</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.768</v>
+        <v>0.7366</v>
       </c>
       <c r="J148" t="n">
-        <v>23.04</v>
+        <v>22.098</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0857</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>2.571</v>
+        <v>2.871</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2445</v>
+        <v>-0.2567</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.335</v>
+        <v>-7.701</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4611</v>
+        <v>-0.4669</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.833</v>
+        <v>-14.007</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.25</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7738</v>
+        <v>0.6989</v>
       </c>
       <c r="J152" t="n">
-        <v>17.0236</v>
+        <v>15.3758</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.75</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2374</v>
+        <v>-0.2616</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.2228</v>
+        <v>-5.7552</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.46</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5098</v>
+        <v>-0.5208</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.2156</v>
+        <v>-11.4576</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.4</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5666</v>
+        <v>-0.5735</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.4652</v>
+        <v>-12.617</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.33</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.633</v>
+        <v>-0.6347</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.926</v>
+        <v>-13.9634</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2853</v>
+        <v>1.268</v>
       </c>
       <c r="J157" t="n">
-        <v>28.2766</v>
+        <v>27.896</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.6</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2152</v>
+        <v>1.193</v>
       </c>
       <c r="J158" t="n">
-        <v>26.7344</v>
+        <v>26.246</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.46</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0499</v>
+        <v>1.0098</v>
       </c>
       <c r="J159" t="n">
-        <v>23.0978</v>
+        <v>22.2156</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.31</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7671</v>
+        <v>0.7393</v>
       </c>
       <c r="J160" t="n">
-        <v>16.8762</v>
+        <v>16.2646</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>1.26</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6522</v>
+        <v>0.6378</v>
       </c>
       <c r="J161" t="n">
-        <v>14.3484</v>
+        <v>14.0316</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>0.97</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1442</v>
+        <v>0.074</v>
       </c>
       <c r="J162" t="n">
-        <v>2.5956</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.52</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.4359</v>
+        <v>-0.4546</v>
       </c>
       <c r="J163" t="n">
-        <v>-7.8462</v>
+        <v>-8.1828</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.51</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.445</v>
+        <v>-0.4632</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.01</v>
+        <v>-8.3376</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.37</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5785</v>
+        <v>-0.5867</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.413</v>
+        <v>-10.5606</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5883</v>
+        <v>-0.5957</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.5894</v>
+        <v>-10.7226</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.95</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5896</v>
+        <v>1.5943</v>
       </c>
       <c r="J167" t="n">
-        <v>28.6128</v>
+        <v>28.6974</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.75</v>
       </c>
       <c r="I168" t="n">
-        <v>1.3686</v>
+        <v>1.3606</v>
       </c>
       <c r="J168" t="n">
-        <v>24.6348</v>
+        <v>24.4908</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.64</v>
       </c>
       <c r="I169" t="n">
-        <v>1.2454</v>
+        <v>1.2288</v>
       </c>
       <c r="J169" t="n">
-        <v>22.4172</v>
+        <v>22.1184</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.41</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9563</v>
+        <v>0.9127</v>
       </c>
       <c r="J170" t="n">
-        <v>17.2134</v>
+        <v>16.4286</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>1.21</v>
       </c>
       <c r="I171" t="n">
-        <v>0.5059</v>
+        <v>0.5125</v>
       </c>
       <c r="J171" t="n">
-        <v>9.106199999999999</v>
+        <v>9.225</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4702/event_4702_evp_summary.xlsx
+++ b/database/event/4702/event_4702_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.2137</v>
+        <v>4.1272</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9506</v>
+        <v>0.9311</v>
       </c>
       <c r="D2" t="n">
-        <v>1.294</v>
+        <v>1.2743</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2137</v>
+        <v>4.1272</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2681</v>
+        <v>3.2404</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9456</v>
+        <v>0.8868</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4279</v>
+        <v>4.476</v>
       </c>
       <c r="I2" t="n">
-        <v>4.542</v>
+        <v>4.5956</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9456</v>
+        <v>0.8868</v>
       </c>
       <c r="K2" t="n">
         <v>113</v>
@@ -529,7 +529,7 @@
         <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4876</v>
+        <v>5.4824</v>
       </c>
       <c r="N2" t="n">
         <v>177</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3615</v>
+        <v>3.348</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7584</v>
+        <v>0.7553</v>
       </c>
       <c r="D3" t="n">
-        <v>0.906</v>
+        <v>0.9194</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3615</v>
+        <v>3.348</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7523</v>
+        <v>2.3046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6092</v>
+        <v>1.0434</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2989</v>
+        <v>2.3313</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3839</v>
+        <v>2.3936</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6092</v>
+        <v>1.0434</v>
       </c>
       <c r="K3" t="n">
         <v>113</v>
@@ -575,7 +575,7 @@
         <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9931</v>
+        <v>3.437</v>
       </c>
       <c r="N3" t="n">
         <v>177</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3536</v>
+        <v>3.3429</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7542</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9024</v>
+        <v>0.9171</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3536</v>
+        <v>3.3429</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3405</v>
+        <v>2.7308</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0131</v>
+        <v>0.6121</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3977</v>
+        <v>3.308</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4595</v>
+        <v>3.3964</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0131</v>
+        <v>0.6121</v>
       </c>
       <c r="K4" t="n">
         <v>113</v>
@@ -621,7 +621,7 @@
         <v>64</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4726</v>
+        <v>4.0085</v>
       </c>
       <c r="N4" t="n">
         <v>177</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0009</v>
+        <v>2.9051</v>
       </c>
       <c r="C5" t="n">
-        <v>0.677</v>
+        <v>0.6554</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7419</v>
+        <v>0.7176</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0009</v>
+        <v>2.9051</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0009</v>
+        <v>2.9051</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.843</v>
+        <v>3.7075</v>
       </c>
       <c r="I5" t="n">
-        <v>3.843</v>
+        <v>3.7075</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.843</v>
+        <v>3.7075</v>
       </c>
       <c r="N5" t="n">
         <v>124</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9675</v>
+        <v>2.8528</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6695</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7267</v>
+        <v>0.6938</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9675</v>
+        <v>2.8528</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9675</v>
+        <v>2.8528</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7699</v>
+        <v>3.5876</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7699</v>
+        <v>3.5876</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7699</v>
+        <v>3.5876</v>
       </c>
       <c r="N6" t="n">
         <v>141</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5838</v>
+        <v>2.5335</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5829</v>
+        <v>0.5716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.552</v>
+        <v>0.5483</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5838</v>
+        <v>2.5335</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5838</v>
+        <v>2.5335</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9301</v>
+        <v>2.856</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9301</v>
+        <v>2.856</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9301</v>
+        <v>2.856</v>
       </c>
       <c r="N7" t="n">
         <v>124</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5293</v>
+        <v>2.505</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5706</v>
+        <v>0.5651</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5272</v>
+        <v>0.5354</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5293</v>
+        <v>2.505</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3207</v>
+        <v>2.2972</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2086</v>
+        <v>0.2078</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3543</v>
+        <v>2.3144</v>
       </c>
       <c r="I8" t="n">
-        <v>2.415</v>
+        <v>2.3762</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2086</v>
+        <v>0.2078</v>
       </c>
       <c r="K8" t="n">
         <v>113</v>
@@ -805,7 +805,7 @@
         <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6236</v>
+        <v>2.584</v>
       </c>
       <c r="N8" t="n">
         <v>177</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5064</v>
+        <v>2.4947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5654</v>
+        <v>0.5628</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5168</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5064</v>
+        <v>2.4947</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5064</v>
+        <v>2.4947</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7607</v>
+        <v>2.7669</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7607</v>
+        <v>2.7669</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7607</v>
+        <v>2.7669</v>
       </c>
       <c r="N9" t="n">
         <v>141</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3749</v>
+        <v>2.3623</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5329</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4569</v>
+        <v>0.4704</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3749</v>
+        <v>2.3623</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3749</v>
+        <v>2.3623</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4729</v>
+        <v>2.4636</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4729</v>
+        <v>2.4636</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4729</v>
+        <v>2.4636</v>
       </c>
       <c r="N10" t="n">
         <v>116</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2219</v>
+        <v>2.236</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5013</v>
+        <v>0.5044</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3873</v>
+        <v>0.4128</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2219</v>
+        <v>2.236</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2219</v>
+        <v>2.236</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2219</v>
+        <v>2.236</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2219</v>
+        <v>2.236</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2219</v>
+        <v>2.236</v>
       </c>
       <c r="N11" t="n">
         <v>124</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1427</v>
+        <v>2.0786</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4834</v>
+        <v>0.4689</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3512</v>
+        <v>0.3411</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1427</v>
+        <v>2.0786</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7383</v>
+        <v>1.7179</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4044</v>
+        <v>0.3607</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7383</v>
+        <v>1.7179</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7383</v>
+        <v>1.7179</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4044</v>
+        <v>0.3607</v>
       </c>
       <c r="K12" t="n">
         <v>117</v>
@@ -989,7 +989,7 @@
         <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1427</v>
+        <v>2.0786</v>
       </c>
       <c r="N12" t="n">
         <v>181</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8642</v>
+        <v>1.8986</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4206</v>
+        <v>0.4283</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2244</v>
+        <v>0.2591</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8642</v>
+        <v>1.8986</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6237</v>
+        <v>1.8986</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7595</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0175</v>
+        <v>1.8986</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0175</v>
+        <v>1.8986</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7595</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="L13" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.258</v>
+        <v>1.8986</v>
       </c>
       <c r="N13" t="n">
-        <v>181</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7953</v>
+        <v>1.8477</v>
       </c>
       <c r="C14" t="n">
-        <v>0.405</v>
+        <v>0.4168</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1931</v>
+        <v>0.2359</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7953</v>
+        <v>1.8477</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7953</v>
+        <v>2.5875</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.7398</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7953</v>
+        <v>2.9796</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7953</v>
+        <v>2.9796</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.7398</v>
       </c>
       <c r="K14" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7953</v>
+        <v>2.2398</v>
       </c>
       <c r="N14" t="n">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7157</v>
+        <v>1.7325</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3871</v>
+        <v>0.3908</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1568</v>
+        <v>0.1834</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7157</v>
+        <v>1.7325</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6339</v>
+        <v>1.6502</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0818</v>
+        <v>0.0823</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6339</v>
+        <v>1.6502</v>
       </c>
       <c r="I15" t="n">
-        <v>1.676</v>
+        <v>1.6943</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0818</v>
+        <v>0.0823</v>
       </c>
       <c r="K15" t="n">
         <v>113</v>
@@ -1127,7 +1127,7 @@
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7578</v>
+        <v>1.7766</v>
       </c>
       <c r="N15" t="n">
         <v>177</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2996</v>
+        <v>1.3278</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2932</v>
+        <v>0.2995</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0326</v>
+        <v>-0.0009</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2996</v>
+        <v>1.3278</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8021</v>
+        <v>0.8672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4975</v>
+        <v>0.4606</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8021</v>
+        <v>0.8672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8021</v>
+        <v>0.8672</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4975</v>
+        <v>0.4606</v>
       </c>
       <c r="K16" t="n">
         <v>117</v>
@@ -1173,7 +1173,7 @@
         <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2996</v>
+        <v>1.3278</v>
       </c>
       <c r="N16" t="n">
         <v>181</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.141</v>
+        <v>1.142</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2574</v>
+        <v>0.2576</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1048</v>
+        <v>-0.0856</v>
       </c>
       <c r="E17" t="n">
-        <v>1.141</v>
+        <v>1.142</v>
       </c>
       <c r="F17" t="n">
-        <v>1.141</v>
+        <v>0.9543</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.1877</v>
       </c>
       <c r="H17" t="n">
-        <v>1.141</v>
+        <v>0.9543</v>
       </c>
       <c r="I17" t="n">
-        <v>1.141</v>
+        <v>0.9543</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.1877</v>
       </c>
       <c r="K17" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>1.141</v>
+        <v>1.142</v>
       </c>
       <c r="N17" t="n">
-        <v>116</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1218</v>
+        <v>1.0494</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2531</v>
+        <v>0.2367</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1135</v>
+        <v>-0.1277</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1218</v>
+        <v>1.0494</v>
       </c>
       <c r="F18" t="n">
-        <v>0.899</v>
+        <v>1.0494</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2228</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.899</v>
+        <v>1.0494</v>
       </c>
       <c r="I18" t="n">
-        <v>0.899</v>
+        <v>1.0494</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2228</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1218</v>
+        <v>1.0494</v>
       </c>
       <c r="N18" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0116</v>
+        <v>0.9809</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2282</v>
+        <v>0.2213</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1637</v>
+        <v>-0.1589</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0116</v>
+        <v>0.9809</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2366</v>
+        <v>1.173</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.225</v>
+        <v>-0.1921</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2366</v>
+        <v>1.173</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2366</v>
+        <v>1.173</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.225</v>
+        <v>-0.1921</v>
       </c>
       <c r="K19" t="n">
         <v>117</v>
@@ -1311,7 +1311,7 @@
         <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0116</v>
+        <v>0.9809000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>181</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8956</v>
+        <v>0.946</v>
       </c>
       <c r="C20" t="n">
-        <v>0.202</v>
+        <v>0.2134</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2165</v>
+        <v>-0.1748</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8956</v>
+        <v>0.946</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8956</v>
+        <v>0.946</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8956</v>
+        <v>0.946</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8956</v>
+        <v>0.946</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8956</v>
+        <v>0.946</v>
       </c>
       <c r="N20" t="n">
         <v>116</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8845</v>
+        <v>0.9164</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1995</v>
+        <v>0.2067</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2216</v>
+        <v>-0.1883</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8845</v>
+        <v>0.9164</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8845</v>
+        <v>0.9164</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8845</v>
+        <v>0.9164</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8845</v>
+        <v>0.9164</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8845</v>
+        <v>0.9164</v>
       </c>
       <c r="N21" t="n">
         <v>116</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6136</v>
+        <v>0.64</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1384</v>
+        <v>0.1444</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3449</v>
+        <v>-0.3142</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6136</v>
+        <v>0.64</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6136</v>
+        <v>0.64</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6136</v>
+        <v>0.64</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6136</v>
+        <v>0.64</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6136</v>
+        <v>0.64</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.2305</v>
+        <v>-0.1435</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.052</v>
+        <v>-0.0324</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7291</v>
+        <v>-0.6712</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2305</v>
+        <v>-0.1435</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2305</v>
+        <v>-0.1435</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2305</v>
+        <v>-0.1435</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2305</v>
+        <v>-0.1435</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2305</v>
+        <v>-0.1435</v>
       </c>
       <c r="N23" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2403</v>
+        <v>-0.1648</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0542</v>
+        <v>-0.0372</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7336</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2403</v>
+        <v>-0.1648</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2403</v>
+        <v>-0.1648</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2403</v>
+        <v>-0.1648</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2403</v>
+        <v>-0.1648</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2403</v>
+        <v>-0.1648</v>
       </c>
       <c r="N24" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3539</v>
+        <v>-0.29</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0798</v>
+        <v>-0.0654</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7853</v>
+        <v>-0.7379</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3539</v>
+        <v>-0.29</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3539</v>
+        <v>-0.29</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3539</v>
+        <v>-0.29</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3539</v>
+        <v>-0.29</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3539</v>
+        <v>-0.29</v>
       </c>
       <c r="N25" t="n">
         <v>141</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7748</v>
+        <v>-0.7416</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1748</v>
+        <v>-0.1673</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9769</v>
+        <v>-0.9436</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7748</v>
+        <v>-0.7416</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7748</v>
+        <v>-0.7416</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7748</v>
+        <v>-0.7416</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7748</v>
+        <v>-0.7416</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7748</v>
+        <v>-0.7416</v>
       </c>
       <c r="N26" t="n">
         <v>141</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1814</v>
+        <v>-0.1754</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9902</v>
+        <v>-0.96</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.3035</v>
+        <v>-1.2513</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2941</v>
+        <v>-0.2823</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.2176</v>
+        <v>-1.1758</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3035</v>
+        <v>-1.2513</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3035</v>
+        <v>-1.2513</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.3035</v>
+        <v>-1.2513</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.3035</v>
+        <v>-1.2513</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.3035</v>
+        <v>-1.2513</v>
       </c>
       <c r="N28" t="n">
         <v>121</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4243</v>
+        <v>-1.4263</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3213</v>
+        <v>-0.3218</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2726</v>
+        <v>-1.2555</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4243</v>
+        <v>-1.4263</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4243</v>
+        <v>-1.4263</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4243</v>
+        <v>-1.4263</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.4243</v>
+        <v>-1.4263</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.4243</v>
+        <v>-1.4263</v>
       </c>
       <c r="N29" t="n">
         <v>121</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.4864</v>
+        <v>-1.5711</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3353</v>
+        <v>-0.3544</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3008</v>
+        <v>-1.3215</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.4864</v>
+        <v>-1.5711</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4864</v>
+        <v>-1.5711</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4864</v>
+        <v>-1.5711</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4864</v>
+        <v>-1.5711</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4864</v>
+        <v>-1.5711</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.7413</v>
+        <v>-1.7124</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3928</v>
+        <v>-0.3863</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.4169</v>
+        <v>-1.3859</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.7413</v>
+        <v>-1.7124</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.7413</v>
+        <v>-1.7124</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.7413</v>
+        <v>-1.7124</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.7413</v>
+        <v>-1.7124</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.7413</v>
+        <v>-1.7124</v>
       </c>
       <c r="N31" t="n">
         <v>121</v>
@@ -1969,10 +1969,10 @@
         <v>1.26</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7078</v>
+        <v>0.6746</v>
       </c>
       <c r="J2" t="n">
-        <v>25.4808</v>
+        <v>24.2856</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1934</v>
+        <v>0.1616</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9624</v>
+        <v>5.8176</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1066</v>
+        <v>-0.0814</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.8376</v>
+        <v>-2.9304</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.97</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.143</v>
+        <v>-0.1131</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.148</v>
+        <v>-4.0716</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1766</v>
+        <v>-0.1433</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.3576</v>
+        <v>-5.1588</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>0.841</v>
+        <v>0.7923</v>
       </c>
       <c r="J7" t="n">
-        <v>30.276</v>
+        <v>28.5228</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.95</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0859</v>
+        <v>-0.0703</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.0924</v>
+        <v>-2.5308</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1353</v>
+        <v>-0.1161</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.8708</v>
+        <v>-4.1796</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1691</v>
+        <v>-0.1488</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.0876</v>
+        <v>-5.3568</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2621</v>
+        <v>-0.2425</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.435600000000001</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.49</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1197</v>
+        <v>1.1248</v>
       </c>
       <c r="J12" t="n">
-        <v>31.3516</v>
+        <v>31.4944</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7522</v>
+        <v>0.7252</v>
       </c>
       <c r="J13" t="n">
-        <v>21.0616</v>
+        <v>20.3056</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7522</v>
+        <v>0.7252</v>
       </c>
       <c r="J14" t="n">
-        <v>21.0616</v>
+        <v>20.3056</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3852</v>
+        <v>0.3511</v>
       </c>
       <c r="J15" t="n">
-        <v>10.7856</v>
+        <v>9.8308</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.626</v>
+        <v>-0.5923</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.528</v>
+        <v>-16.5844</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6328</v>
+        <v>0.5799</v>
       </c>
       <c r="J17" t="n">
-        <v>17.7184</v>
+        <v>16.2372</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3919</v>
+        <v>0.3378</v>
       </c>
       <c r="J18" t="n">
-        <v>10.9732</v>
+        <v>9.458399999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1391</v>
+        <v>-0.1218</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.8948</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4366</v>
+        <v>-0.4291</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.2248</v>
+        <v>-12.0148</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4974</v>
+        <v>-0.4973</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.9272</v>
+        <v>-13.9244</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.68</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3176</v>
+        <v>1.3377</v>
       </c>
       <c r="J22" t="n">
-        <v>34.2576</v>
+        <v>34.7802</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.59</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2016</v>
+        <v>1.2168</v>
       </c>
       <c r="J23" t="n">
-        <v>31.2416</v>
+        <v>31.6368</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8516</v>
+        <v>0.8357</v>
       </c>
       <c r="J24" t="n">
-        <v>22.1416</v>
+        <v>21.7282</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4626</v>
+        <v>0.4314</v>
       </c>
       <c r="J25" t="n">
-        <v>12.0276</v>
+        <v>11.2164</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6887</v>
+        <v>-0.6624</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.9062</v>
+        <v>-17.2224</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4809</v>
+        <v>0.4324</v>
       </c>
       <c r="J27" t="n">
-        <v>12.5034</v>
+        <v>11.2424</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1059</v>
+        <v>-0.0917</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.7534</v>
+        <v>-2.3842</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2627</v>
+        <v>-0.2451</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.8302</v>
+        <v>-6.3726</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3188</v>
+        <v>-0.3023</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.2888</v>
+        <v>-7.8598</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5748</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.716</v>
+        <v>-14.9448</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>0.97</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0146</v>
+        <v>-0.0015</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3066</v>
+        <v>-0.0315</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0723</v>
+        <v>-0.0566</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.5183</v>
+        <v>-1.1886</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.78</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2423</v>
+        <v>-0.2278</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.0883</v>
+        <v>-4.7838</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.49</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.5011</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.5525</v>
+        <v>-10.5231</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.32</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.6714</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.6437</v>
+        <v>-14.0994</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.65</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2551</v>
+        <v>1.2743</v>
       </c>
       <c r="J37" t="n">
-        <v>26.3571</v>
+        <v>26.7603</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.58</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1672</v>
+        <v>1.1845</v>
       </c>
       <c r="J38" t="n">
-        <v>24.5112</v>
+        <v>24.8745</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.52</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0909</v>
+        <v>1.1069</v>
       </c>
       <c r="J39" t="n">
-        <v>22.9089</v>
+        <v>23.2449</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8168</v>
+        <v>0.8054</v>
       </c>
       <c r="J40" t="n">
-        <v>17.1528</v>
+        <v>16.9134</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>1.21</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5305</v>
+        <v>0.5028</v>
       </c>
       <c r="J41" t="n">
-        <v>11.1405</v>
+        <v>10.5588</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.88</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5272</v>
+        <v>1.5607</v>
       </c>
       <c r="J42" t="n">
-        <v>29.0168</v>
+        <v>29.6533</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.55</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1252</v>
+        <v>1.1434</v>
       </c>
       <c r="J43" t="n">
-        <v>21.3788</v>
+        <v>21.7246</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.4</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9055</v>
+        <v>0.9022</v>
       </c>
       <c r="J44" t="n">
-        <v>17.2045</v>
+        <v>17.1418</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.887</v>
+        <v>0.8822</v>
       </c>
       <c r="J45" t="n">
-        <v>16.853</v>
+        <v>16.7618</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.3</v>
       </c>
       <c r="I46" t="n">
-        <v>0.713</v>
+        <v>0.6956</v>
       </c>
       <c r="J46" t="n">
-        <v>13.547</v>
+        <v>13.2164</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>0.78</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2139</v>
+        <v>-0.1966</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.0641</v>
+        <v>-3.7354</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>0.65</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3456</v>
+        <v>-0.337</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.5664</v>
+        <v>-6.403</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.59</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3998</v>
+        <v>-0.3931</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.5962</v>
+        <v>-7.4689</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.59</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3998</v>
+        <v>-0.3931</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.5962</v>
+        <v>-7.4689</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.26</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6889</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.0891</v>
+        <v>-13.6078</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8566</v>
+        <v>0.805</v>
       </c>
       <c r="J52" t="n">
-        <v>25.698</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.33</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5628</v>
       </c>
       <c r="J53" t="n">
-        <v>18.675</v>
+        <v>16.884</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.97</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0646</v>
+        <v>-0.0507</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.938</v>
+        <v>-1.521</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2397</v>
+        <v>-0.2198</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.191</v>
+        <v>-6.594</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2498</v>
+        <v>-0.2302</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.494</v>
+        <v>-6.906</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.39</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7212</v>
+        <v>0.6641</v>
       </c>
       <c r="J57" t="n">
-        <v>21.636</v>
+        <v>19.923</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5372</v>
+        <v>0.4775</v>
       </c>
       <c r="J58" t="n">
-        <v>16.116</v>
+        <v>14.325</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.09</v>
+        <v>-0.0735</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.7</v>
+        <v>-2.205</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.95</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.09</v>
+        <v>-0.0735</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.7</v>
+        <v>-2.205</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3611</v>
+        <v>-0.3478</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.833</v>
+        <v>-10.434</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.01</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0663</v>
+        <v>0.0473</v>
       </c>
       <c r="J62" t="n">
-        <v>1.989</v>
+        <v>1.419</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0315</v>
+        <v>-0.0242</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.945</v>
+        <v>-0.726</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.9</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1374</v>
+        <v>-0.1208</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.122</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3072</v>
+        <v>-0.2896</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.215999999999999</v>
+        <v>-8.688000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3072</v>
+        <v>-0.2896</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.215999999999999</v>
+        <v>-8.688000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.64</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2953</v>
+        <v>1.3157</v>
       </c>
       <c r="J67" t="n">
-        <v>38.859</v>
+        <v>39.471</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6728</v>
+        <v>0.6415</v>
       </c>
       <c r="J68" t="n">
-        <v>20.184</v>
+        <v>19.245</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.13</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3873</v>
+        <v>0.3527</v>
       </c>
       <c r="J69" t="n">
-        <v>11.619</v>
+        <v>10.581</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1712</v>
+        <v>0.1449</v>
       </c>
       <c r="J70" t="n">
-        <v>5.136</v>
+        <v>4.347</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.456</v>
+        <v>-0.4152</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.68</v>
+        <v>-12.456</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0613</v>
+        <v>1.0461</v>
       </c>
       <c r="J72" t="n">
-        <v>28.6551</v>
+        <v>28.2447</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2521</v>
+        <v>0.2057</v>
       </c>
       <c r="J73" t="n">
-        <v>6.8067</v>
+        <v>5.5539</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.77</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.282</v>
+        <v>-0.2632</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.614</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.76</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2916</v>
+        <v>-0.2733</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.8732</v>
+        <v>-7.3791</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3011</v>
+        <v>-0.2833</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.1297</v>
+        <v>-7.6491</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.6</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2416</v>
+        <v>1.2588</v>
       </c>
       <c r="J77" t="n">
-        <v>33.5232</v>
+        <v>33.9876</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8743</v>
+        <v>0.855</v>
       </c>
       <c r="J78" t="n">
-        <v>23.6061</v>
+        <v>23.085</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.27</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6932</v>
+        <v>0.6627</v>
       </c>
       <c r="J79" t="n">
-        <v>18.7164</v>
+        <v>17.8929</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4309</v>
+        <v>-0.3899</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.6343</v>
+        <v>-10.5273</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.85</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5058</v>
+        <v>-0.4664</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.6566</v>
+        <v>-12.5928</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1404</v>
+        <v>0.1068</v>
       </c>
       <c r="J82" t="n">
-        <v>4.212</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.04</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1404</v>
+        <v>0.1068</v>
       </c>
       <c r="J83" t="n">
-        <v>4.212</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1509</v>
+        <v>-0.1325</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.527</v>
+        <v>-3.975</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1831</v>
+        <v>-0.1635</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.493</v>
+        <v>-4.905</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3115</v>
+        <v>-0.294</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.345000000000001</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.54</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9143</v>
+        <v>0.8653</v>
       </c>
       <c r="J87" t="n">
-        <v>27.429</v>
+        <v>25.959</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.4</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7167</v>
+        <v>0.6585</v>
       </c>
       <c r="J88" t="n">
-        <v>21.501</v>
+        <v>19.755</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0825</v>
+        <v>-0.0667</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.475</v>
+        <v>-2.001</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1093</v>
+        <v>-0.0914</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.279</v>
+        <v>-2.742</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.273</v>
+        <v>-0.2547</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.19</v>
+        <v>-7.641</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.71</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3249</v>
+        <v>1.3472</v>
       </c>
       <c r="J92" t="n">
-        <v>25.1731</v>
+        <v>25.5968</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.6</v>
       </c>
       <c r="I93" t="n">
-        <v>1.189</v>
+        <v>1.2075</v>
       </c>
       <c r="J93" t="n">
-        <v>22.591</v>
+        <v>22.9425</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.6</v>
       </c>
       <c r="I94" t="n">
-        <v>1.189</v>
+        <v>1.2075</v>
       </c>
       <c r="J94" t="n">
-        <v>22.591</v>
+        <v>22.9425</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.29</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6945</v>
+        <v>0.6758</v>
       </c>
       <c r="J95" t="n">
-        <v>13.1955</v>
+        <v>12.8402</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>1.26</v>
       </c>
       <c r="I96" t="n">
-        <v>0.633</v>
+        <v>0.6105</v>
       </c>
       <c r="J96" t="n">
-        <v>12.027</v>
+        <v>11.5995</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>0.77</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.2421</v>
+        <v>-0.228</v>
       </c>
       <c r="J97" t="n">
-        <v>-4.5999</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3201</v>
+        <v>-0.3087</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.0819</v>
+        <v>-5.8653</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.59</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4071</v>
+        <v>-0.3979</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.7349</v>
+        <v>-7.5601</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.59</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4071</v>
+        <v>-0.3979</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.7349</v>
+        <v>-7.5601</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4246</v>
+        <v>-0.4163</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.067399999999999</v>
+        <v>-7.9097</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.07</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2239</v>
+        <v>0.1815</v>
       </c>
       <c r="J102" t="n">
-        <v>5.8214</v>
+        <v>4.719</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.01</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0694</v>
+        <v>0.0501</v>
       </c>
       <c r="J103" t="n">
-        <v>1.8044</v>
+        <v>1.3026</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2389</v>
+        <v>-0.2199</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.2114</v>
+        <v>-5.7174</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2487</v>
+        <v>-0.2297</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.4662</v>
+        <v>-5.9722</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4064</v>
+        <v>-0.3956</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.5664</v>
+        <v>-10.2856</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.45</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0293</v>
+        <v>1.0315</v>
       </c>
       <c r="J107" t="n">
-        <v>26.7618</v>
+        <v>26.819</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0137</v>
+        <v>1.0133</v>
       </c>
       <c r="J108" t="n">
-        <v>26.3562</v>
+        <v>26.3458</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6066</v>
+        <v>0.5746</v>
       </c>
       <c r="J109" t="n">
-        <v>15.7716</v>
+        <v>14.9396</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1377</v>
+        <v>-0.1106</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.5802</v>
+        <v>-2.8756</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.98</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1377</v>
+        <v>-0.1106</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.5802</v>
+        <v>-2.8756</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3831</v>
+        <v>0.3308</v>
       </c>
       <c r="J112" t="n">
-        <v>9.577500000000001</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0467</v>
+        <v>-0.0373</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.1675</v>
+        <v>-0.9325</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1588</v>
+        <v>-0.1414</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.97</v>
+        <v>-3.535</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.67</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.362</v>
+        <v>-0.3476</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.050000000000001</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3801</v>
+        <v>-0.3671</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.5025</v>
+        <v>-9.1775</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3878</v>
+        <v>1.4124</v>
       </c>
       <c r="J117" t="n">
-        <v>34.695</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6409</v>
+        <v>0.6135</v>
       </c>
       <c r="J118" t="n">
-        <v>16.0225</v>
+        <v>15.3375</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6202</v>
+        <v>0.5921</v>
       </c>
       <c r="J119" t="n">
-        <v>15.505</v>
+        <v>14.8025</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.16</v>
       </c>
       <c r="I120" t="n">
-        <v>0.444</v>
+        <v>0.4121</v>
       </c>
       <c r="J120" t="n">
-        <v>11.1</v>
+        <v>10.3025</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.05</v>
       </c>
       <c r="I121" t="n">
-        <v>0.155</v>
+        <v>0.129</v>
       </c>
       <c r="J121" t="n">
-        <v>3.875</v>
+        <v>3.225</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.03</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1512</v>
+        <v>0.122</v>
       </c>
       <c r="J122" t="n">
-        <v>3.4776</v>
+        <v>2.806</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>0.77</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2612</v>
+        <v>-0.2441</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.0076</v>
+        <v>-5.6143</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.77</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2612</v>
+        <v>-0.2441</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.0076</v>
+        <v>-5.6143</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.326</v>
+        <v>-0.3101</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.498</v>
+        <v>-7.1323</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3625</v>
+        <v>-0.3483</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.3375</v>
+        <v>-8.010899999999999</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.71</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3574</v>
+        <v>1.3798</v>
       </c>
       <c r="J127" t="n">
-        <v>31.2202</v>
+        <v>31.7354</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5962</v>
+        <v>0.5682</v>
       </c>
       <c r="J128" t="n">
-        <v>13.7126</v>
+        <v>13.0686</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5749</v>
+        <v>0.5462</v>
       </c>
       <c r="J129" t="n">
-        <v>13.2227</v>
+        <v>12.5626</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5091</v>
+        <v>0.4788</v>
       </c>
       <c r="J130" t="n">
-        <v>11.7093</v>
+        <v>11.0124</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>1.19</v>
       </c>
       <c r="I131" t="n">
-        <v>0.5091</v>
+        <v>0.4788</v>
       </c>
       <c r="J131" t="n">
-        <v>11.7093</v>
+        <v>11.0124</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>0.76</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.202</v>
+        <v>-0.1764</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.04</v>
+        <v>-3.528</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>0.63</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3419</v>
+        <v>-0.3332</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.838</v>
+        <v>-6.664</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.43</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5228</v>
+        <v>-0.5249</v>
       </c>
       <c r="J134" t="n">
-        <v>-10.456</v>
+        <v>-10.498</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.33</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6127</v>
+        <v>-0.6248</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.254</v>
+        <v>-12.496</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.28</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6586</v>
+        <v>-0.6784</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.172</v>
+        <v>-13.568</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>2.05</v>
       </c>
       <c r="I137" t="n">
-        <v>1.7018</v>
+        <v>1.7497</v>
       </c>
       <c r="J137" t="n">
-        <v>34.036</v>
+        <v>34.994</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.9</v>
       </c>
       <c r="I138" t="n">
-        <v>1.531</v>
+        <v>1.5665</v>
       </c>
       <c r="J138" t="n">
-        <v>30.62</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.61</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1907</v>
+        <v>1.2137</v>
       </c>
       <c r="J139" t="n">
-        <v>23.814</v>
+        <v>24.274</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8672</v>
       </c>
       <c r="J140" t="n">
-        <v>17.41</v>
+        <v>17.344</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>1.21</v>
       </c>
       <c r="I141" t="n">
-        <v>0.5073</v>
+        <v>0.4776</v>
       </c>
       <c r="J141" t="n">
-        <v>10.146</v>
+        <v>9.552</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.88</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6371</v>
+        <v>1.6951</v>
       </c>
       <c r="J142" t="n">
-        <v>49.113</v>
+        <v>50.853</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2983</v>
+        <v>0.2626</v>
       </c>
       <c r="J143" t="n">
-        <v>8.949</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3355</v>
+        <v>-0.2935</v>
       </c>
       <c r="J144" t="n">
-        <v>-10.065</v>
+        <v>-8.805</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3889</v>
+        <v>-0.3461</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.667</v>
+        <v>-10.383</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.75</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7208</v>
+        <v>-0.6911</v>
       </c>
       <c r="J146" t="n">
-        <v>-21.624</v>
+        <v>-20.733</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7954</v>
+        <v>0.7416</v>
       </c>
       <c r="J147" t="n">
-        <v>23.862</v>
+        <v>22.248</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7366</v>
+        <v>0.6801</v>
       </c>
       <c r="J148" t="n">
-        <v>22.098</v>
+        <v>20.403</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="J149" t="n">
-        <v>2.871</v>
+        <v>2.154</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2567</v>
+        <v>-0.2371</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.701</v>
+        <v>-7.113</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4669</v>
+        <v>-0.4648</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.007</v>
+        <v>-13.944</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.25</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6989</v>
+        <v>0.6983</v>
       </c>
       <c r="J152" t="n">
-        <v>15.3758</v>
+        <v>15.3626</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.75</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2616</v>
+        <v>-0.2482</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.7552</v>
+        <v>-5.4604</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.46</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5208</v>
+        <v>-0.5213</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.4576</v>
+        <v>-11.4686</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.4</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5735</v>
+        <v>-0.5812</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.617</v>
+        <v>-12.7864</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.33</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6347</v>
+        <v>-0.6526</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.9634</v>
+        <v>-14.3572</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>1.268</v>
+        <v>1.2876</v>
       </c>
       <c r="J157" t="n">
-        <v>27.896</v>
+        <v>28.3272</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.6</v>
       </c>
       <c r="I158" t="n">
-        <v>1.193</v>
+        <v>1.2105</v>
       </c>
       <c r="J158" t="n">
-        <v>26.246</v>
+        <v>26.631</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.46</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0098</v>
+        <v>1.0173</v>
       </c>
       <c r="J159" t="n">
-        <v>22.2156</v>
+        <v>22.3806</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.31</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7393</v>
+        <v>0.7227</v>
       </c>
       <c r="J160" t="n">
-        <v>16.2646</v>
+        <v>15.8994</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>1.26</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6378</v>
+        <v>0.6152</v>
       </c>
       <c r="J161" t="n">
-        <v>14.0316</v>
+        <v>13.5344</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>0.97</v>
       </c>
       <c r="I162" t="n">
-        <v>0.074</v>
+        <v>0.1276</v>
       </c>
       <c r="J162" t="n">
-        <v>1.332</v>
+        <v>2.2968</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.52</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.4546</v>
+        <v>-0.4509</v>
       </c>
       <c r="J163" t="n">
-        <v>-8.1828</v>
+        <v>-8.116199999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.51</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4632</v>
+        <v>-0.4598</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.3376</v>
+        <v>-8.276400000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.37</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5867</v>
+        <v>-0.5955</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.5606</v>
+        <v>-10.719</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5957</v>
+        <v>-0.6057</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.7226</v>
+        <v>-10.9026</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.95</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5943</v>
+        <v>1.6334</v>
       </c>
       <c r="J167" t="n">
-        <v>28.6974</v>
+        <v>29.4012</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.75</v>
       </c>
       <c r="I168" t="n">
-        <v>1.3606</v>
+        <v>1.3866</v>
       </c>
       <c r="J168" t="n">
-        <v>24.4908</v>
+        <v>24.9588</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.64</v>
       </c>
       <c r="I169" t="n">
-        <v>1.2288</v>
+        <v>1.2511</v>
       </c>
       <c r="J169" t="n">
-        <v>22.1184</v>
+        <v>22.5198</v>
       </c>
     </row>
     <row r="170">
@@ -8729,10 +8729,10 @@
         <v>1.21</v>
       </c>
       <c r="I171" t="n">
-        <v>0.5125</v>
+        <v>0.4835</v>
       </c>
       <c r="J171" t="n">
-        <v>9.225</v>
+        <v>8.702999999999999</v>
       </c>
     </row>
   </sheetData>
